--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="708">
   <si>
     <t>Datum</t>
   </si>
@@ -1929,25 +1929,43 @@
     <t>Makula Radek</t>
   </si>
   <si>
+    <t>38:00</t>
+  </si>
+  <si>
+    <t>29:00</t>
+  </si>
+  <si>
+    <t>Vychivskyi Volodymyr</t>
+  </si>
+  <si>
+    <t>63:00</t>
+  </si>
+  <si>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Kačena Stanislav</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>Nováková Adéla</t>
+  </si>
+  <si>
+    <t>69:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>29:00</t>
-  </si>
-  <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>10 min 34 s</t>
+    <t>11 min 02 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13226,7 +13244,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46147.0</v>
+        <v>46154.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -14097,13 +14115,13 @@
         <v>Prosek</v>
       </c>
       <c r="C1" s="107">
-        <v>46146.0</v>
+        <v>46143.0</v>
       </c>
       <c r="D1" s="108" t="s">
         <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46146.0</v>
+        <v>46173.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14128,18 +14146,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.5035271535192989</v>
+        <v>0.32496139858532447</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>16679.0</v>
+        <v>270705.0</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>7789.0</v>
+        <v>97298.0</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14147,12 +14165,12 @@
       <c r="A3" s="117"/>
       <c r="B3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Pátek</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Neděle</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14161,7 +14179,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>1196.0</v>
+        <v>51342.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14181,7 +14199,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>1969.0</v>
+        <v>51506.0</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14205,7 +14223,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>3302.0</v>
+        <v>33154.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14225,7 +14243,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>0.0</v>
+        <v>1314.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14233,14 +14251,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14304,14 +14322,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>0.0</v>
+        <v>-1937.0</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>1512.0</v>
+        <v>24234.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14321,7 +14339,7 @@
         <v>635</v>
       </c>
       <c r="C10" s="145">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="145" t="s">
         <v>636</v>
@@ -14329,10 +14347,18 @@
       <c r="E10" s="146" t="s">
         <v>637</v>
       </c>
-      <c r="F10" s="144"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="147"/>
+      <c r="F10" s="144" t="s">
+        <v>638</v>
+      </c>
+      <c r="G10" s="145">
+        <v>5.0</v>
+      </c>
+      <c r="H10" s="145" t="s">
+        <v>639</v>
+      </c>
+      <c r="I10" s="147">
+        <v>32.0</v>
+      </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
       <c r="L10" s="142" t="s">
@@ -14346,38 +14372,52 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="143"/>
       <c r="B11" s="144" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C11" s="145">
+        <v>4.0</v>
+      </c>
+      <c r="D11" s="145" t="s">
+        <v>636</v>
+      </c>
+      <c r="E11" s="146" t="s">
+        <v>641</v>
+      </c>
+      <c r="F11" s="144" t="s">
+        <v>642</v>
+      </c>
+      <c r="G11" s="145">
         <v>1.0</v>
       </c>
-      <c r="D11" s="145" t="s">
-        <v>639</v>
-      </c>
-      <c r="E11" s="146" t="s">
-        <v>640</v>
-      </c>
-      <c r="F11" s="144"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="147"/>
+      <c r="H11" s="145" t="s">
+        <v>643</v>
+      </c>
+      <c r="I11" s="147">
+        <v>3.0</v>
+      </c>
       <c r="J11" s="35"/>
       <c r="K11" s="20"/>
       <c r="L11" s="148" t="s">
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>911.0</v>
+        <v>6262.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="145"/>
+      <c r="B12" s="144" t="s">
+        <v>644</v>
+      </c>
+      <c r="C12" s="145">
+        <v>6.0</v>
+      </c>
+      <c r="D12" s="145" t="s">
+        <v>645</v>
+      </c>
       <c r="E12" s="146" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14397,7 +14437,7 @@
       <c r="C13" s="145"/>
       <c r="D13" s="145"/>
       <c r="E13" s="146" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14409,7 +14449,7 @@
         <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
@@ -14419,7 +14459,7 @@
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
       <c r="E14" s="146" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14441,7 +14481,7 @@
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
       <c r="E15" s="146" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14473,7 +14513,7 @@
         <v>611</v>
       </c>
       <c r="M16" s="120">
-        <v>0.0</v>
+        <v>863.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
@@ -14493,7 +14533,7 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>0.0</v>
+        <v>1095.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14564,16 +14604,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="K21" s="165">
-        <v>329.0</v>
+        <v>2838.0</v>
       </c>
       <c r="L21" s="166">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14628,16 +14668,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K24" s="166">
-        <v>46.0</v>
+        <v>655.0</v>
       </c>
       <c r="L24" s="166">
-        <v>5.0</v>
+        <v>65.0</v>
       </c>
       <c r="M24" s="173">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14690,14 +14730,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.2</v>
+        <v>0.0821969696969697</v>
       </c>
       <c r="M27" s="180">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14748,10 +14788,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8</v>
+        <v>0.9178030303030302</v>
       </c>
       <c r="M30" s="184">
-        <v>0.2</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14902,8 +14942,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="185"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -14965,7 +15005,7 @@
       <c r="B5" s="186"/>
       <c r="C5" s="186"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="185"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -14999,7 +15039,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="186"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="185"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -15032,7 +15072,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="186"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="185"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -15099,7 +15139,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="186"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="185"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -15139,7 +15179,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="K10" s="185"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -15167,7 +15207,7 @@
       <c r="B11" s="4"/>
       <c r="C11" s="186"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="185"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -15206,7 +15246,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="185"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -15302,7 +15342,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="186"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="185"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -15404,7 +15444,7 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="185"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -15438,7 +15478,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="185"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15540,7 +15580,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="185"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -15574,7 +15614,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="185"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15648,7 +15688,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="185"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -15811,7 +15851,7 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="185"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -15879,13 +15919,13 @@
       <c r="B32" s="4"/>
       <c r="C32" s="186"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="185"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="185"/>
+      <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
@@ -15913,7 +15953,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="185"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -15947,7 +15987,7 @@
       <c r="B34" s="4"/>
       <c r="C34" s="186"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="185"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -16083,13 +16123,13 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="185"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-      <c r="K38" s="185"/>
+      <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
@@ -16108,6 +16148,7 @@
       <c r="AA38" s="185"/>
       <c r="AB38" s="185"/>
       <c r="AC38" s="185"/>
+      <c r="AD38" s="185"/>
       <c r="AE38" s="185"/>
       <c r="AF38" s="185"/>
     </row>
@@ -16116,7 +16157,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="185"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16183,7 +16224,7 @@
       <c r="B41" s="4"/>
       <c r="C41" s="186"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="185"/>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -16285,7 +16326,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="186"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="185"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -16319,7 +16360,7 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="185"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -16451,22 +16492,22 @@
       <c r="AF48" s="185"/>
     </row>
     <row r="49">
-      <c r="A49" s="185"/>
-      <c r="B49" s="185"/>
-      <c r="C49" s="187"/>
-      <c r="D49" s="185"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="186"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="185"/>
-      <c r="F49" s="185"/>
-      <c r="G49" s="185"/>
-      <c r="H49" s="185"/>
-      <c r="I49" s="185"/>
-      <c r="J49" s="185"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="185"/>
-      <c r="L49" s="185"/>
-      <c r="M49" s="185"/>
-      <c r="N49" s="185"/>
-      <c r="O49" s="185"/>
-      <c r="P49" s="185"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
       <c r="Q49" s="185"/>
       <c r="R49" s="185"/>
       <c r="S49" s="185"/>
@@ -16485,22 +16526,22 @@
       <c r="AF49" s="185"/>
     </row>
     <row r="50">
-      <c r="A50" s="185"/>
-      <c r="B50" s="185"/>
-      <c r="C50" s="187"/>
-      <c r="D50" s="185"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="186"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="185"/>
-      <c r="F50" s="185"/>
-      <c r="G50" s="185"/>
-      <c r="H50" s="185"/>
-      <c r="I50" s="185"/>
-      <c r="J50" s="185"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
       <c r="K50" s="185"/>
-      <c r="L50" s="185"/>
-      <c r="M50" s="185"/>
-      <c r="N50" s="185"/>
-      <c r="O50" s="185"/>
-      <c r="P50" s="185"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
       <c r="Q50" s="185"/>
       <c r="R50" s="185"/>
       <c r="S50" s="185"/>
@@ -16519,22 +16560,22 @@
       <c r="AF50" s="185"/>
     </row>
     <row r="51">
-      <c r="A51" s="185"/>
-      <c r="B51" s="185"/>
-      <c r="C51" s="187"/>
-      <c r="D51" s="185"/>
-      <c r="E51" s="185"/>
-      <c r="F51" s="185"/>
-      <c r="G51" s="185"/>
-      <c r="H51" s="185"/>
-      <c r="I51" s="185"/>
-      <c r="J51" s="185"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="186"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
       <c r="K51" s="185"/>
-      <c r="L51" s="185"/>
-      <c r="M51" s="185"/>
-      <c r="N51" s="185"/>
-      <c r="O51" s="185"/>
-      <c r="P51" s="185"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
       <c r="Q51" s="185"/>
       <c r="R51" s="185"/>
       <c r="S51" s="185"/>
@@ -16553,22 +16594,22 @@
       <c r="AF51" s="185"/>
     </row>
     <row r="52">
-      <c r="A52" s="185"/>
-      <c r="B52" s="187"/>
-      <c r="C52" s="187"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="185"/>
-      <c r="F52" s="185"/>
-      <c r="G52" s="185"/>
-      <c r="H52" s="185"/>
-      <c r="I52" s="185"/>
-      <c r="J52" s="185"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="186"/>
+      <c r="C52" s="186"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
       <c r="K52" s="185"/>
-      <c r="L52" s="185"/>
-      <c r="M52" s="185"/>
-      <c r="N52" s="185"/>
-      <c r="O52" s="185"/>
-      <c r="P52" s="185"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
       <c r="Q52" s="185"/>
       <c r="R52" s="185"/>
       <c r="S52" s="185"/>
@@ -16587,22 +16628,22 @@
       <c r="AF52" s="185"/>
     </row>
     <row r="53">
-      <c r="A53" s="185"/>
-      <c r="B53" s="185"/>
-      <c r="C53" s="187"/>
-      <c r="D53" s="185"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="186"/>
+      <c r="D53" s="4"/>
       <c r="E53" s="185"/>
-      <c r="F53" s="185"/>
-      <c r="G53" s="185"/>
-      <c r="H53" s="185"/>
-      <c r="I53" s="185"/>
-      <c r="J53" s="185"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
       <c r="K53" s="185"/>
-      <c r="L53" s="185"/>
-      <c r="M53" s="185"/>
-      <c r="N53" s="185"/>
-      <c r="O53" s="185"/>
-      <c r="P53" s="185"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
       <c r="Q53" s="185"/>
       <c r="R53" s="185"/>
       <c r="S53" s="185"/>
@@ -16621,22 +16662,22 @@
       <c r="AF53" s="185"/>
     </row>
     <row r="54">
-      <c r="A54" s="185"/>
-      <c r="B54" s="185"/>
-      <c r="C54" s="187"/>
-      <c r="D54" s="185"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="186"/>
+      <c r="D54" s="4"/>
       <c r="E54" s="185"/>
-      <c r="F54" s="185"/>
-      <c r="G54" s="185"/>
-      <c r="H54" s="185"/>
-      <c r="I54" s="185"/>
-      <c r="J54" s="185"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
       <c r="K54" s="185"/>
-      <c r="L54" s="185"/>
-      <c r="M54" s="185"/>
-      <c r="N54" s="185"/>
-      <c r="O54" s="185"/>
-      <c r="P54" s="185"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
       <c r="Q54" s="185"/>
       <c r="R54" s="185"/>
       <c r="S54" s="185"/>
@@ -16655,22 +16696,22 @@
       <c r="AF54" s="185"/>
     </row>
     <row r="55">
-      <c r="A55" s="185"/>
-      <c r="B55" s="185"/>
-      <c r="C55" s="187"/>
-      <c r="D55" s="185"/>
-      <c r="E55" s="185"/>
-      <c r="F55" s="185"/>
-      <c r="G55" s="185"/>
-      <c r="H55" s="185"/>
-      <c r="I55" s="185"/>
-      <c r="J55" s="185"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="186"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
       <c r="K55" s="185"/>
-      <c r="L55" s="185"/>
-      <c r="M55" s="185"/>
-      <c r="N55" s="185"/>
-      <c r="O55" s="185"/>
-      <c r="P55" s="185"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
       <c r="Q55" s="185"/>
       <c r="R55" s="185"/>
       <c r="S55" s="185"/>
@@ -16689,22 +16730,22 @@
       <c r="AF55" s="185"/>
     </row>
     <row r="56">
-      <c r="A56" s="185"/>
-      <c r="B56" s="185"/>
-      <c r="C56" s="187"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="185"/>
-      <c r="F56" s="185"/>
-      <c r="G56" s="185"/>
-      <c r="H56" s="185"/>
-      <c r="I56" s="185"/>
-      <c r="J56" s="185"/>
-      <c r="K56" s="185"/>
-      <c r="L56" s="185"/>
-      <c r="M56" s="185"/>
-      <c r="N56" s="185"/>
-      <c r="O56" s="185"/>
-      <c r="P56" s="185"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="186"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
       <c r="Q56" s="185"/>
       <c r="R56" s="185"/>
       <c r="S56" s="185"/>
@@ -16723,22 +16764,22 @@
       <c r="AF56" s="185"/>
     </row>
     <row r="57">
-      <c r="A57" s="185"/>
-      <c r="B57" s="185"/>
-      <c r="C57" s="187"/>
-      <c r="D57" s="185"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="186"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="185"/>
-      <c r="F57" s="185"/>
-      <c r="G57" s="185"/>
-      <c r="H57" s="185"/>
-      <c r="I57" s="185"/>
-      <c r="J57" s="185"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
       <c r="K57" s="185"/>
-      <c r="L57" s="185"/>
-      <c r="M57" s="185"/>
-      <c r="N57" s="185"/>
-      <c r="O57" s="185"/>
-      <c r="P57" s="185"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
       <c r="Q57" s="185"/>
       <c r="R57" s="185"/>
       <c r="S57" s="185"/>
@@ -17158,6 +17199,7 @@
       <c r="AA69" s="185"/>
       <c r="AB69" s="185"/>
       <c r="AC69" s="185"/>
+      <c r="AD69" s="185"/>
       <c r="AE69" s="185"/>
       <c r="AF69" s="185"/>
     </row>
@@ -18093,6 +18135,7 @@
       <c r="AA97" s="185"/>
       <c r="AB97" s="185"/>
       <c r="AC97" s="185"/>
+      <c r="AD97" s="185"/>
       <c r="AE97" s="185"/>
       <c r="AF97" s="185"/>
     </row>
@@ -18453,6 +18496,7 @@
       <c r="AA108" s="185"/>
       <c r="AB108" s="185"/>
       <c r="AC108" s="185"/>
+      <c r="AD108" s="185"/>
       <c r="AE108" s="185"/>
       <c r="AF108" s="185"/>
     </row>
@@ -18642,8 +18686,311 @@
       <c r="AE114" s="185"/>
       <c r="AF114" s="185"/>
     </row>
+    <row r="115">
+      <c r="A115" s="185"/>
+      <c r="B115" s="185"/>
+      <c r="C115" s="185"/>
+      <c r="D115" s="185"/>
+      <c r="E115" s="185"/>
+      <c r="F115" s="185"/>
+      <c r="G115" s="185"/>
+      <c r="H115" s="185"/>
+      <c r="I115" s="185"/>
+      <c r="J115" s="185"/>
+      <c r="K115" s="185"/>
+      <c r="L115" s="185"/>
+      <c r="M115" s="185"/>
+      <c r="O115" s="185"/>
+      <c r="P115" s="185"/>
+      <c r="Q115" s="185"/>
+      <c r="S115" s="185"/>
+      <c r="T115" s="185"/>
+      <c r="U115" s="185"/>
+      <c r="V115" s="185"/>
+      <c r="W115" s="185"/>
+      <c r="X115" s="185"/>
+      <c r="Y115" s="185"/>
+      <c r="Z115" s="185"/>
+      <c r="AB115" s="185"/>
+      <c r="AC115" s="185"/>
+      <c r="AE115" s="185"/>
+      <c r="AF115" s="185"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="185"/>
+      <c r="B116" s="185"/>
+      <c r="C116" s="185"/>
+      <c r="D116" s="185"/>
+      <c r="E116" s="185"/>
+      <c r="F116" s="185"/>
+      <c r="G116" s="185"/>
+      <c r="H116" s="185"/>
+      <c r="I116" s="185"/>
+      <c r="J116" s="185"/>
+      <c r="K116" s="185"/>
+      <c r="L116" s="185"/>
+      <c r="M116" s="185"/>
+      <c r="O116" s="185"/>
+      <c r="P116" s="185"/>
+      <c r="Q116" s="185"/>
+      <c r="S116" s="185"/>
+      <c r="T116" s="185"/>
+      <c r="U116" s="185"/>
+      <c r="V116" s="185"/>
+      <c r="W116" s="185"/>
+      <c r="X116" s="185"/>
+      <c r="Y116" s="185"/>
+      <c r="Z116" s="185"/>
+      <c r="AB116" s="185"/>
+      <c r="AC116" s="185"/>
+      <c r="AE116" s="185"/>
+      <c r="AF116" s="185"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="185"/>
+      <c r="B117" s="185"/>
+      <c r="C117" s="185"/>
+      <c r="D117" s="185"/>
+      <c r="E117" s="185"/>
+      <c r="F117" s="185"/>
+      <c r="G117" s="185"/>
+      <c r="H117" s="185"/>
+      <c r="I117" s="185"/>
+      <c r="J117" s="185"/>
+      <c r="K117" s="185"/>
+      <c r="L117" s="185"/>
+      <c r="M117" s="185"/>
+      <c r="N117" s="185"/>
+      <c r="O117" s="185"/>
+      <c r="P117" s="185"/>
+      <c r="Q117" s="185"/>
+      <c r="S117" s="185"/>
+      <c r="T117" s="185"/>
+      <c r="U117" s="185"/>
+      <c r="V117" s="185"/>
+      <c r="W117" s="185"/>
+      <c r="X117" s="185"/>
+      <c r="Y117" s="185"/>
+      <c r="Z117" s="185"/>
+      <c r="AB117" s="185"/>
+      <c r="AC117" s="185"/>
+      <c r="AE117" s="185"/>
+      <c r="AF117" s="185"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="185"/>
+      <c r="B118" s="185"/>
+      <c r="C118" s="185"/>
+      <c r="D118" s="185"/>
+      <c r="E118" s="185"/>
+      <c r="F118" s="185"/>
+      <c r="G118" s="185"/>
+      <c r="H118" s="185"/>
+      <c r="I118" s="185"/>
+      <c r="J118" s="185"/>
+      <c r="K118" s="185"/>
+      <c r="L118" s="185"/>
+      <c r="M118" s="185"/>
+      <c r="O118" s="185"/>
+      <c r="P118" s="185"/>
+      <c r="Q118" s="185"/>
+      <c r="S118" s="185"/>
+      <c r="T118" s="185"/>
+      <c r="U118" s="185"/>
+      <c r="V118" s="185"/>
+      <c r="W118" s="185"/>
+      <c r="X118" s="185"/>
+      <c r="Y118" s="185"/>
+      <c r="Z118" s="185"/>
+      <c r="AB118" s="185"/>
+      <c r="AC118" s="185"/>
+      <c r="AE118" s="185"/>
+      <c r="AF118" s="185"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="185"/>
+      <c r="B119" s="185"/>
+      <c r="C119" s="185"/>
+      <c r="D119" s="185"/>
+      <c r="E119" s="185"/>
+      <c r="F119" s="185"/>
+      <c r="G119" s="185"/>
+      <c r="H119" s="185"/>
+      <c r="I119" s="185"/>
+      <c r="J119" s="185"/>
+      <c r="K119" s="185"/>
+      <c r="L119" s="185"/>
+      <c r="M119" s="185"/>
+      <c r="O119" s="185"/>
+      <c r="P119" s="185"/>
+      <c r="Q119" s="185"/>
+      <c r="S119" s="185"/>
+      <c r="T119" s="185"/>
+      <c r="U119" s="185"/>
+      <c r="V119" s="185"/>
+      <c r="W119" s="185"/>
+      <c r="X119" s="185"/>
+      <c r="Y119" s="185"/>
+      <c r="Z119" s="185"/>
+      <c r="AB119" s="185"/>
+      <c r="AC119" s="185"/>
+      <c r="AE119" s="185"/>
+      <c r="AF119" s="185"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="185"/>
+      <c r="B120" s="185"/>
+      <c r="C120" s="185"/>
+      <c r="D120" s="185"/>
+      <c r="E120" s="185"/>
+      <c r="F120" s="185"/>
+      <c r="G120" s="185"/>
+      <c r="H120" s="185"/>
+      <c r="I120" s="185"/>
+      <c r="J120" s="185"/>
+      <c r="K120" s="185"/>
+      <c r="L120" s="185"/>
+      <c r="M120" s="185"/>
+      <c r="O120" s="185"/>
+      <c r="P120" s="185"/>
+      <c r="Q120" s="185"/>
+      <c r="S120" s="185"/>
+      <c r="T120" s="185"/>
+      <c r="U120" s="185"/>
+      <c r="V120" s="185"/>
+      <c r="W120" s="185"/>
+      <c r="X120" s="185"/>
+      <c r="Y120" s="185"/>
+      <c r="Z120" s="185"/>
+      <c r="AB120" s="185"/>
+      <c r="AC120" s="185"/>
+      <c r="AE120" s="185"/>
+      <c r="AF120" s="185"/>
+    </row>
     <row r="121">
+      <c r="A121" s="185"/>
+      <c r="B121" s="185"/>
       <c r="C121" s="187"/>
+      <c r="D121" s="185"/>
+      <c r="E121" s="185"/>
+      <c r="F121" s="185"/>
+      <c r="G121" s="185"/>
+      <c r="H121" s="185"/>
+      <c r="I121" s="185"/>
+      <c r="J121" s="185"/>
+      <c r="K121" s="185"/>
+      <c r="L121" s="185"/>
+      <c r="M121" s="185"/>
+      <c r="N121" s="185"/>
+      <c r="O121" s="185"/>
+      <c r="P121" s="185"/>
+      <c r="Q121" s="185"/>
+      <c r="R121" s="185"/>
+      <c r="S121" s="185"/>
+      <c r="T121" s="185"/>
+      <c r="U121" s="185"/>
+      <c r="V121" s="185"/>
+      <c r="W121" s="185"/>
+      <c r="X121" s="185"/>
+      <c r="Y121" s="185"/>
+      <c r="Z121" s="185"/>
+      <c r="AA121" s="185"/>
+      <c r="AB121" s="185"/>
+      <c r="AC121" s="185"/>
+      <c r="AE121" s="185"/>
+      <c r="AF121" s="185"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="185"/>
+      <c r="B122" s="185"/>
+      <c r="C122" s="185"/>
+      <c r="D122" s="185"/>
+      <c r="E122" s="185"/>
+      <c r="F122" s="185"/>
+      <c r="G122" s="185"/>
+      <c r="H122" s="185"/>
+      <c r="I122" s="185"/>
+      <c r="J122" s="185"/>
+      <c r="K122" s="185"/>
+      <c r="L122" s="185"/>
+      <c r="M122" s="185"/>
+      <c r="O122" s="185"/>
+      <c r="P122" s="185"/>
+      <c r="Q122" s="185"/>
+      <c r="S122" s="185"/>
+      <c r="T122" s="185"/>
+      <c r="U122" s="185"/>
+      <c r="V122" s="185"/>
+      <c r="W122" s="185"/>
+      <c r="X122" s="185"/>
+      <c r="Y122" s="185"/>
+      <c r="Z122" s="185"/>
+      <c r="AB122" s="185"/>
+      <c r="AC122" s="185"/>
+      <c r="AE122" s="185"/>
+      <c r="AF122" s="185"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="185"/>
+      <c r="B123" s="185"/>
+      <c r="C123" s="185"/>
+      <c r="D123" s="185"/>
+      <c r="E123" s="185"/>
+      <c r="F123" s="185"/>
+      <c r="G123" s="185"/>
+      <c r="H123" s="185"/>
+      <c r="I123" s="185"/>
+      <c r="J123" s="185"/>
+      <c r="K123" s="185"/>
+      <c r="L123" s="185"/>
+      <c r="M123" s="185"/>
+      <c r="N123" s="185"/>
+      <c r="O123" s="185"/>
+      <c r="P123" s="185"/>
+      <c r="Q123" s="185"/>
+      <c r="S123" s="185"/>
+      <c r="T123" s="185"/>
+      <c r="U123" s="185"/>
+      <c r="V123" s="185"/>
+      <c r="W123" s="185"/>
+      <c r="X123" s="185"/>
+      <c r="Y123" s="185"/>
+      <c r="Z123" s="185"/>
+      <c r="AB123" s="185"/>
+      <c r="AC123" s="185"/>
+      <c r="AE123" s="185"/>
+      <c r="AF123" s="185"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="185"/>
+      <c r="B124" s="185"/>
+      <c r="C124" s="185"/>
+      <c r="D124" s="185"/>
+      <c r="E124" s="185"/>
+      <c r="F124" s="185"/>
+      <c r="G124" s="185"/>
+      <c r="H124" s="185"/>
+      <c r="I124" s="185"/>
+      <c r="J124" s="185"/>
+      <c r="K124" s="185"/>
+      <c r="L124" s="185"/>
+      <c r="M124" s="185"/>
+      <c r="N124" s="185"/>
+      <c r="O124" s="185"/>
+      <c r="P124" s="185"/>
+      <c r="Q124" s="185"/>
+      <c r="S124" s="185"/>
+      <c r="T124" s="185"/>
+      <c r="U124" s="185"/>
+      <c r="V124" s="185"/>
+      <c r="W124" s="185"/>
+      <c r="X124" s="185"/>
+      <c r="Y124" s="185"/>
+      <c r="Z124" s="185"/>
+      <c r="AB124" s="185"/>
+      <c r="AC124" s="185"/>
+      <c r="AE124" s="185"/>
+      <c r="AF124" s="185"/>
     </row>
     <row r="128">
       <c r="C128" s="187"/>
@@ -18819,10 +19166,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -21177,14 +21524,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kuzníková Nicol")</f>
-        <v>Kuzníková Nicol</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -21202,8 +21543,8 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W42" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -23111,7 +23452,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
         <v>Zličín</v>
       </c>
-      <c r="F81" s="2"/>
+      <c r="F81" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -23128,8 +23472,8 @@
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
       <c r="V81" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W81" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -23739,14 +24083,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D92" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Killiakov Andrei")</f>
-        <v>Killiakov Andrei</v>
-      </c>
-      <c r="E92" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -23764,8 +24102,8 @@
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W92" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24802,8 +25140,8 @@
       <c r="T110" s="2"/>
       <c r="U110" s="2"/>
       <c r="V110" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W110" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25401,10 +25739,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D121" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Přibyl Jan")</f>
-        <v>Přibyl Jan</v>
-      </c>
+      <c r="D121" s="2"/>
       <c r="E121" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
@@ -25515,14 +25850,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D123" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hrach Michal")</f>
-        <v>Hrach Michal</v>
-      </c>
-      <c r="E123" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -25540,8 +25869,8 @@
       <c r="T123" s="2"/>
       <c r="U123" s="2"/>
       <c r="V123" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W123" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25572,14 +25901,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D124" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kvapil Filip Leon")</f>
-        <v>Kvapil Filip Leon</v>
-      </c>
-      <c r="E124" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -25597,8 +25920,8 @@
       <c r="T124" s="2"/>
       <c r="U124" s="2"/>
       <c r="V124" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W124" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25686,14 +26009,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Irena Kovacsova")</f>
-        <v>Irena Kovacsova</v>
-      </c>
-      <c r="E126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -25711,8 +26028,8 @@
       <c r="T126" s="2"/>
       <c r="U126" s="2"/>
       <c r="V126" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.784)</f>
-        <v>224.784</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W126" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -60627,7 +60944,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -60659,28 +60976,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -60709,22 +61026,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -60746,20 +61063,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -60783,18 +61100,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -60821,15 +61138,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -60856,14 +61173,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -60887,14 +61204,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -60919,17 +61236,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -60954,14 +61271,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61174,7 +61491,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61499,7 +61816,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -61620,7 +61937,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -61739,7 +62056,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -61773,7 +62090,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -61865,7 +62182,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62044,7 +62361,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62165,7 +62482,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62373,7 +62690,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62494,7 +62811,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -62702,7 +63019,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63171,7 +63488,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63205,7 +63522,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63239,7 +63556,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63273,7 +63590,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63366,7 +63683,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -63632,7 +63949,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -63666,7 +63983,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -63758,7 +64075,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -63821,7 +64138,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -63913,7 +64230,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -63947,7 +64264,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -63981,7 +64298,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64044,7 +64361,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64136,7 +64453,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64199,7 +64516,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64320,7 +64637,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64471,7 +64788,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -64856,7 +65173,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="717">
   <si>
     <t>Datum</t>
   </si>
@@ -1929,7 +1929,7 @@
     <t>Makula Radek</t>
   </si>
   <si>
-    <t>38:00</t>
+    <t>52:00</t>
   </si>
   <si>
     <t>29:00</t>
@@ -1938,34 +1938,61 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>63:00</t>
+    <t>120:00</t>
   </si>
   <si>
     <t>Šebesta Tomáš</t>
   </si>
   <si>
+    <t>56:00</t>
+  </si>
+  <si>
     <t>23:00</t>
   </si>
   <si>
     <t>Kačena Stanislav</t>
   </si>
   <si>
-    <t>6:00</t>
+    <t>19:00</t>
   </si>
   <si>
     <t>Nováková Adéla</t>
   </si>
   <si>
-    <t>69:00</t>
+    <t>133:00</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
+    <t>Hanibal Filip</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>Kopic Jakub</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>Putna Jaroslav</t>
+  </si>
+  <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>11 min 02 s</t>
+    <t>Ahurieva Viktoriia</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>Gorol Patrik</t>
+  </si>
+  <si>
+    <t>11 min 50 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13244,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46154.0</v>
+        <v>46162.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13293,7 +13320,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13804,7 +13831,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="86">
         <f t="shared" si="3"/>
@@ -13845,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="86">
         <f t="shared" si="3"/>
@@ -14081,7 +14108,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Nováková Adéla,Makula Radek,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
+      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
       <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan,Kulinič Michail,Kačena Stanislav"</formula1>
@@ -14121,7 +14148,7 @@
         <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46173.0</v>
+        <v>46160.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14146,18 +14173,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.32496139858532447</v>
+        <v>0.34210884172421985</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>270705.0</v>
+        <v>570148.7999999999</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>97298.0</v>
+        <v>202875.4</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14170,7 +14197,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Pondělí</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14179,7 +14206,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>51342.0</v>
+        <v>103527.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14199,7 +14226,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>51506.0</v>
+        <v>106114.0</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14223,7 +14250,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>33154.0</v>
+        <v>77921.90000000001</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14243,7 +14270,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>1314.0</v>
+        <v>6797.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14251,14 +14278,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>145</v>
+        <v>292.5</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14322,14 +14349,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>-1937.0</v>
+        <v>4.499999999989086</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>24234.0</v>
+        <v>44490.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14339,7 +14366,7 @@
         <v>635</v>
       </c>
       <c r="C10" s="145">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D10" s="145" t="s">
         <v>636</v>
@@ -14351,13 +14378,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="H10" s="145" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>32.0</v>
+        <v>77.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14375,25 +14402,25 @@
         <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F11" s="144" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G11" s="145">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H11" s="145" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I11" s="147">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="J11" s="35"/>
       <c r="K11" s="20"/>
@@ -14401,28 +14428,36 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>6262.0</v>
+        <v>21730.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C12" s="145">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>646</v>
-      </c>
-      <c r="F12" s="144"/>
-      <c r="G12" s="145"/>
-      <c r="H12" s="145"/>
-      <c r="I12" s="147"/>
+        <v>647</v>
+      </c>
+      <c r="F12" s="144" t="s">
+        <v>648</v>
+      </c>
+      <c r="G12" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="145" t="s">
+        <v>649</v>
+      </c>
+      <c r="I12" s="147">
+        <v>3.0</v>
+      </c>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
@@ -14433,11 +14468,17 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
+      <c r="B13" s="144" t="s">
+        <v>650</v>
+      </c>
+      <c r="C13" s="145">
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="145" t="s">
+        <v>651</v>
+      </c>
       <c r="E13" s="146" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14455,11 +14496,17 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
-      <c r="B14" s="144"/>
-      <c r="C14" s="145"/>
-      <c r="D14" s="145"/>
+      <c r="B14" s="144" t="s">
+        <v>652</v>
+      </c>
+      <c r="C14" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="145" t="s">
+        <v>653</v>
+      </c>
       <c r="E14" s="146" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14477,11 +14524,17 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="143"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
+      <c r="B15" s="144" t="s">
+        <v>654</v>
+      </c>
+      <c r="C15" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="145" t="s">
+        <v>655</v>
+      </c>
       <c r="E15" s="146" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14493,15 +14546,21 @@
         <v>610</v>
       </c>
       <c r="M15" s="120">
-        <v>0.0</v>
+        <v>71.0</v>
       </c>
       <c r="N15" s="116"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="143"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
+      <c r="B16" s="144" t="s">
+        <v>656</v>
+      </c>
+      <c r="C16" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="145" t="s">
+        <v>653</v>
+      </c>
       <c r="E16" s="152"/>
       <c r="F16" s="144"/>
       <c r="G16" s="145"/>
@@ -14513,7 +14572,7 @@
         <v>611</v>
       </c>
       <c r="M16" s="120">
-        <v>863.0</v>
+        <v>1647.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
@@ -14533,7 +14592,7 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>1095.0</v>
+        <v>3280.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14604,16 +14663,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="K21" s="165">
-        <v>2838.0</v>
+        <v>8428.0</v>
       </c>
       <c r="L21" s="166">
-        <v>5.0</v>
+        <v>24.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14668,16 +14727,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="K24" s="166">
-        <v>655.0</v>
+        <v>1363.0</v>
       </c>
       <c r="L24" s="166">
-        <v>65.0</v>
+        <v>169.0</v>
       </c>
       <c r="M24" s="173">
-        <v>3.0</v>
+        <v>21.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14730,14 +14789,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.0821969696969697</v>
+        <v>0.12405159314875214</v>
       </c>
       <c r="M27" s="180">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14788,10 +14847,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.9178030303030302</v>
+        <v>0.8759484068512479</v>
       </c>
       <c r="M30" s="184">
-        <v>0.03636363636363636</v>
+        <v>0.06908715639365795</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14937,7 +14996,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="186"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="185"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -14971,7 +15030,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="186"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="185"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15005,7 +15064,7 @@
       <c r="B5" s="186"/>
       <c r="C5" s="186"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="185"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -15072,13 +15131,13 @@
       <c r="B7" s="4"/>
       <c r="C7" s="186"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="185"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="185"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -15097,6 +15156,7 @@
       <c r="AA7" s="185"/>
       <c r="AB7" s="185"/>
       <c r="AC7" s="185"/>
+      <c r="AD7" s="185"/>
       <c r="AE7" s="185"/>
       <c r="AF7" s="185"/>
     </row>
@@ -15179,7 +15239,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="185"/>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -15246,7 +15306,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="K12" s="185"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -15376,7 +15436,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="186"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="185"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -15410,7 +15470,7 @@
       <c r="B17" s="186"/>
       <c r="C17" s="186"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="185"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -15444,7 +15504,7 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="185"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -15512,7 +15572,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="186"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="185"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -15654,7 +15714,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="185"/>
+      <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -15682,7 +15742,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="185"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15716,7 +15776,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="185"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15755,7 +15815,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="185"/>
+      <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -15783,7 +15843,7 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="185"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -15817,7 +15877,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="185"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15919,13 +15979,13 @@
       <c r="B32" s="4"/>
       <c r="C32" s="186"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="185"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
+      <c r="K32" s="185"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
@@ -15959,7 +16019,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="185"/>
+      <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16027,7 +16087,7 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="185"/>
+      <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
@@ -16061,7 +16121,7 @@
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
+      <c r="K36" s="185"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
@@ -16089,7 +16149,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="186"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="185"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -16129,7 +16189,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
+      <c r="K38" s="185"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
@@ -16197,7 +16257,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="185"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16264,7 +16324,7 @@
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="K42" s="185"/>
+      <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
@@ -16394,7 +16454,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="186"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="185"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -16468,7 +16528,7 @@
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
+      <c r="K48" s="185"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -16564,7 +16624,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="185"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16598,7 +16658,7 @@
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="185"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -16632,7 +16692,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="185"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16666,7 +16726,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="186"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="185"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -16700,7 +16760,7 @@
       <c r="B55" s="4"/>
       <c r="C55" s="186"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
+      <c r="E55" s="185"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -16734,13 +16794,13 @@
       <c r="B56" s="4"/>
       <c r="C56" s="186"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
+      <c r="E56" s="185"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
+      <c r="K56" s="185"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
@@ -16798,22 +16858,22 @@
       <c r="AF57" s="185"/>
     </row>
     <row r="58">
-      <c r="A58" s="185"/>
-      <c r="B58" s="185"/>
-      <c r="C58" s="187"/>
-      <c r="D58" s="185"/>
-      <c r="E58" s="185"/>
-      <c r="F58" s="185"/>
-      <c r="G58" s="185"/>
-      <c r="H58" s="185"/>
-      <c r="I58" s="185"/>
-      <c r="J58" s="185"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="186"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
       <c r="K58" s="185"/>
-      <c r="L58" s="185"/>
-      <c r="M58" s="185"/>
-      <c r="N58" s="185"/>
-      <c r="O58" s="185"/>
-      <c r="P58" s="185"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
       <c r="Q58" s="185"/>
       <c r="R58" s="185"/>
       <c r="S58" s="185"/>
@@ -16832,22 +16892,22 @@
       <c r="AF58" s="185"/>
     </row>
     <row r="59">
-      <c r="A59" s="185"/>
-      <c r="B59" s="185"/>
-      <c r="C59" s="187"/>
-      <c r="D59" s="185"/>
-      <c r="E59" s="185"/>
-      <c r="F59" s="185"/>
-      <c r="G59" s="185"/>
-      <c r="H59" s="185"/>
-      <c r="I59" s="185"/>
-      <c r="J59" s="185"/>
-      <c r="K59" s="185"/>
-      <c r="L59" s="185"/>
-      <c r="M59" s="185"/>
-      <c r="N59" s="185"/>
-      <c r="O59" s="185"/>
-      <c r="P59" s="185"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="186"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
       <c r="Q59" s="185"/>
       <c r="R59" s="185"/>
       <c r="S59" s="185"/>
@@ -16866,22 +16926,22 @@
       <c r="AF59" s="185"/>
     </row>
     <row r="60">
-      <c r="A60" s="185"/>
-      <c r="B60" s="185"/>
-      <c r="C60" s="187"/>
-      <c r="D60" s="185"/>
-      <c r="E60" s="185"/>
-      <c r="F60" s="185"/>
-      <c r="G60" s="185"/>
-      <c r="H60" s="185"/>
-      <c r="I60" s="185"/>
-      <c r="J60" s="185"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="186"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
       <c r="K60" s="185"/>
-      <c r="L60" s="185"/>
-      <c r="M60" s="185"/>
-      <c r="N60" s="185"/>
-      <c r="O60" s="185"/>
-      <c r="P60" s="185"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
       <c r="Q60" s="185"/>
       <c r="R60" s="185"/>
       <c r="S60" s="185"/>
@@ -16900,22 +16960,22 @@
       <c r="AF60" s="185"/>
     </row>
     <row r="61">
-      <c r="A61" s="185"/>
-      <c r="B61" s="185"/>
-      <c r="C61" s="187"/>
-      <c r="D61" s="185"/>
-      <c r="E61" s="185"/>
-      <c r="F61" s="185"/>
-      <c r="G61" s="185"/>
-      <c r="H61" s="185"/>
-      <c r="I61" s="185"/>
-      <c r="J61" s="185"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="186"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
       <c r="K61" s="185"/>
-      <c r="L61" s="185"/>
-      <c r="M61" s="185"/>
-      <c r="N61" s="185"/>
-      <c r="O61" s="185"/>
-      <c r="P61" s="185"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
       <c r="Q61" s="185"/>
       <c r="R61" s="185"/>
       <c r="S61" s="185"/>
@@ -16934,22 +16994,22 @@
       <c r="AF61" s="185"/>
     </row>
     <row r="62">
-      <c r="A62" s="185"/>
-      <c r="B62" s="185"/>
-      <c r="C62" s="187"/>
-      <c r="D62" s="185"/>
-      <c r="E62" s="185"/>
-      <c r="F62" s="185"/>
-      <c r="G62" s="185"/>
-      <c r="H62" s="185"/>
-      <c r="I62" s="185"/>
-      <c r="J62" s="185"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="186"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
       <c r="K62" s="185"/>
-      <c r="L62" s="185"/>
-      <c r="M62" s="185"/>
-      <c r="N62" s="185"/>
-      <c r="O62" s="185"/>
-      <c r="P62" s="185"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
       <c r="Q62" s="185"/>
       <c r="R62" s="185"/>
       <c r="S62" s="185"/>
@@ -16968,22 +17028,22 @@
       <c r="AF62" s="185"/>
     </row>
     <row r="63">
-      <c r="A63" s="185"/>
-      <c r="B63" s="185"/>
-      <c r="C63" s="187"/>
-      <c r="D63" s="185"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="186"/>
+      <c r="D63" s="4"/>
       <c r="E63" s="185"/>
-      <c r="F63" s="185"/>
-      <c r="G63" s="185"/>
-      <c r="H63" s="185"/>
-      <c r="I63" s="185"/>
-      <c r="J63" s="185"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
       <c r="K63" s="185"/>
-      <c r="L63" s="185"/>
-      <c r="M63" s="185"/>
-      <c r="N63" s="185"/>
-      <c r="O63" s="185"/>
-      <c r="P63" s="185"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
       <c r="Q63" s="185"/>
       <c r="R63" s="185"/>
       <c r="S63" s="185"/>
@@ -17002,22 +17062,22 @@
       <c r="AF63" s="185"/>
     </row>
     <row r="64">
-      <c r="A64" s="185"/>
-      <c r="B64" s="185"/>
-      <c r="C64" s="187"/>
-      <c r="D64" s="185"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="186"/>
+      <c r="D64" s="4"/>
       <c r="E64" s="185"/>
-      <c r="F64" s="185"/>
-      <c r="G64" s="185"/>
-      <c r="H64" s="185"/>
-      <c r="I64" s="185"/>
-      <c r="J64" s="185"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
       <c r="K64" s="185"/>
-      <c r="L64" s="185"/>
-      <c r="M64" s="185"/>
-      <c r="N64" s="185"/>
-      <c r="O64" s="185"/>
-      <c r="P64" s="185"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
       <c r="Q64" s="185"/>
       <c r="R64" s="185"/>
       <c r="S64" s="185"/>
@@ -17602,6 +17662,7 @@
       <c r="AA81" s="185"/>
       <c r="AB81" s="185"/>
       <c r="AC81" s="185"/>
+      <c r="AD81" s="185"/>
       <c r="AE81" s="185"/>
       <c r="AF81" s="185"/>
     </row>
@@ -18547,6 +18608,7 @@
       <c r="K110" s="185"/>
       <c r="L110" s="185"/>
       <c r="M110" s="185"/>
+      <c r="N110" s="185"/>
       <c r="O110" s="185"/>
       <c r="P110" s="185"/>
       <c r="Q110" s="185"/>
@@ -18670,9 +18732,11 @@
       <c r="K114" s="185"/>
       <c r="L114" s="185"/>
       <c r="M114" s="185"/>
+      <c r="N114" s="185"/>
       <c r="O114" s="185"/>
       <c r="P114" s="185"/>
       <c r="Q114" s="185"/>
+      <c r="R114" s="185"/>
       <c r="S114" s="185"/>
       <c r="T114" s="185"/>
       <c r="U114" s="185"/>
@@ -18681,8 +18745,10 @@
       <c r="X114" s="185"/>
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
+      <c r="AA114" s="185"/>
       <c r="AB114" s="185"/>
       <c r="AC114" s="185"/>
+      <c r="AD114" s="185"/>
       <c r="AE114" s="185"/>
       <c r="AF114" s="185"/>
     </row>
@@ -18700,6 +18766,7 @@
       <c r="K115" s="185"/>
       <c r="L115" s="185"/>
       <c r="M115" s="185"/>
+      <c r="N115" s="185"/>
       <c r="O115" s="185"/>
       <c r="P115" s="185"/>
       <c r="Q115" s="185"/>
@@ -18730,9 +18797,11 @@
       <c r="K116" s="185"/>
       <c r="L116" s="185"/>
       <c r="M116" s="185"/>
+      <c r="N116" s="185"/>
       <c r="O116" s="185"/>
       <c r="P116" s="185"/>
       <c r="Q116" s="185"/>
+      <c r="R116" s="185"/>
       <c r="S116" s="185"/>
       <c r="T116" s="185"/>
       <c r="U116" s="185"/>
@@ -18741,6 +18810,7 @@
       <c r="X116" s="185"/>
       <c r="Y116" s="185"/>
       <c r="Z116" s="185"/>
+      <c r="AA116" s="185"/>
       <c r="AB116" s="185"/>
       <c r="AC116" s="185"/>
       <c r="AE116" s="185"/>
@@ -18764,6 +18834,7 @@
       <c r="O117" s="185"/>
       <c r="P117" s="185"/>
       <c r="Q117" s="185"/>
+      <c r="R117" s="185"/>
       <c r="S117" s="185"/>
       <c r="T117" s="185"/>
       <c r="U117" s="185"/>
@@ -18772,6 +18843,7 @@
       <c r="X117" s="185"/>
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
+      <c r="AA117" s="185"/>
       <c r="AB117" s="185"/>
       <c r="AC117" s="185"/>
       <c r="AE117" s="185"/>
@@ -18791,9 +18863,11 @@
       <c r="K118" s="185"/>
       <c r="L118" s="185"/>
       <c r="M118" s="185"/>
+      <c r="N118" s="185"/>
       <c r="O118" s="185"/>
       <c r="P118" s="185"/>
       <c r="Q118" s="185"/>
+      <c r="R118" s="185"/>
       <c r="S118" s="185"/>
       <c r="T118" s="185"/>
       <c r="U118" s="185"/>
@@ -18802,6 +18876,7 @@
       <c r="X118" s="185"/>
       <c r="Y118" s="185"/>
       <c r="Z118" s="185"/>
+      <c r="AA118" s="185"/>
       <c r="AB118" s="185"/>
       <c r="AC118" s="185"/>
       <c r="AE118" s="185"/>
@@ -18821,6 +18896,7 @@
       <c r="K119" s="185"/>
       <c r="L119" s="185"/>
       <c r="M119" s="185"/>
+      <c r="N119" s="185"/>
       <c r="O119" s="185"/>
       <c r="P119" s="185"/>
       <c r="Q119" s="185"/>
@@ -18851,6 +18927,7 @@
       <c r="K120" s="185"/>
       <c r="L120" s="185"/>
       <c r="M120" s="185"/>
+      <c r="N120" s="185"/>
       <c r="O120" s="185"/>
       <c r="P120" s="185"/>
       <c r="Q120" s="185"/>
@@ -19166,10 +19243,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -19440,8 +19517,8 @@
         <v>Malešice</v>
       </c>
       <c r="G8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="H8" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -19802,7 +19879,7 @@
       </c>
       <c r="B14" s="192" t="str">
         <f>IF(OR(E14=Report!$B$1, F14=Report!$B$1, G14=Report!$B$1, H14=Report!$B$1), D14, "")</f>
-        <v/>
+        <v>Coufal Jakub</v>
       </c>
       <c r="C14" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -19820,7 +19897,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="G14" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -20840,7 +20920,7 @@
       </c>
       <c r="B31" s="192" t="str">
         <f>IF(OR(E31=Report!$B$1, F31=Report!$B$1, G31=Report!$B$1, H31=Report!$B$1), D31, "")</f>
-        <v/>
+        <v>Gorol Patrik</v>
       </c>
       <c r="C31" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -20858,7 +20938,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G31" s="2"/>
+      <c r="G31" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -23925,7 +24008,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H89" s="2"/>
+      <c r="H89" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -26009,8 +26095,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
+      <c r="D126" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pavel Břicháč")</f>
+        <v>Pavel Břicháč</v>
+      </c>
+      <c r="E126" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -26028,8 +26120,8 @@
       <c r="T126" s="2"/>
       <c r="U126" s="2"/>
       <c r="V126" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W126" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -60944,7 +61036,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -60976,28 +61068,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61026,22 +61118,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61063,20 +61155,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61100,18 +61192,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61138,15 +61230,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61173,14 +61265,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61204,14 +61296,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61236,17 +61328,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61271,14 +61363,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61491,7 +61583,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61816,7 +61908,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -61937,7 +62029,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62056,7 +62148,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62090,7 +62182,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62182,7 +62274,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62361,7 +62453,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62482,7 +62574,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62690,7 +62782,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62811,7 +62903,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63019,7 +63111,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63488,7 +63580,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63522,7 +63614,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63556,7 +63648,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63590,7 +63682,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63683,7 +63775,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -63949,7 +64041,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -63983,7 +64075,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64075,7 +64167,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64138,7 +64230,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64230,7 +64322,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64264,7 +64356,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64298,7 +64390,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64361,7 +64453,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64453,7 +64545,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64516,7 +64608,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64637,7 +64729,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64788,7 +64880,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65173,7 +65265,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="717">
   <si>
     <t>Datum</t>
   </si>
@@ -1938,13 +1938,13 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>120:00</t>
+    <t>148:00</t>
   </si>
   <si>
     <t>Šebesta Tomáš</t>
   </si>
   <si>
-    <t>56:00</t>
+    <t>79:00</t>
   </si>
   <si>
     <t>23:00</t>
@@ -1959,9 +1959,6 @@
     <t>Nováková Adéla</t>
   </si>
   <si>
-    <t>133:00</t>
-  </si>
-  <si>
     <t>13:00</t>
   </si>
   <si>
@@ -1986,13 +1983,16 @@
     <t>Ahurieva Viktoriia</t>
   </si>
   <si>
-    <t>15:00</t>
+    <t>22:00</t>
   </si>
   <si>
     <t>Gorol Patrik</t>
   </si>
   <si>
-    <t>11 min 50 s</t>
+    <t>Coufal Jakub</t>
+  </si>
+  <si>
+    <t>11 min 51 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13271,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46162.0</v>
+        <v>46164.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13320,7 +13320,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Pátek</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -14108,7 +14108,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
+      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
       <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan,Kulinič Michail,Kačena Stanislav"</formula1>
@@ -14148,7 +14148,7 @@
         <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46160.0</v>
+        <v>46173.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14173,18 +14173,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.34210884172421985</v>
+        <v>0.35111359105567275</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>570148.7999999999</v>
+        <v>652567.7999999999</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>202875.4</v>
+        <v>233113.5</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14197,7 +14197,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Neděle</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14206,7 +14206,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>103527.0</v>
+        <v>118961.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14226,7 +14226,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>106114.0</v>
+        <v>115758.0</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14250,7 +14250,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>77921.90000000001</v>
+        <v>90413.3</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14270,7 +14270,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>6797.0</v>
+        <v>8211.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14278,14 +14278,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>292.5</v>
+        <v>344.5</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14349,14 +14349,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>4.499999999989086</v>
+        <v>6.999999999989086</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>44490.0</v>
+        <v>51318.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14378,13 +14378,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="H10" s="145" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>77.0</v>
+        <v>92.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14402,7 +14402,7 @@
         <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D11" s="145" t="s">
         <v>641</v>
@@ -14428,7 +14428,7 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>21730.0</v>
+        <v>26427.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
@@ -14438,22 +14438,22 @@
         <v>645</v>
       </c>
       <c r="C12" s="145">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D12" s="145" t="s">
+        <v>639</v>
+      </c>
+      <c r="E12" s="146" t="s">
         <v>646</v>
       </c>
-      <c r="E12" s="146" t="s">
+      <c r="F12" s="144" t="s">
         <v>647</v>
-      </c>
-      <c r="F12" s="144" t="s">
-        <v>648</v>
       </c>
       <c r="G12" s="145">
         <v>1.0</v>
       </c>
       <c r="H12" s="145" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I12" s="147">
         <v>3.0</v>
@@ -14469,16 +14469,16 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
       <c r="B13" s="144" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C13" s="145">
         <v>3.0</v>
       </c>
       <c r="D13" s="145" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E13" s="146" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14490,23 +14490,23 @@
         <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>1700.0</v>
+        <v>2700.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
       <c r="B14" s="144" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C14" s="145">
         <v>1.0</v>
       </c>
       <c r="D14" s="145" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E14" s="146" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14525,16 +14525,16 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="143"/>
       <c r="B15" s="144" t="s">
+        <v>653</v>
+      </c>
+      <c r="C15" s="145">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="145" t="s">
         <v>654</v>
       </c>
-      <c r="C15" s="145">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="145" t="s">
-        <v>655</v>
-      </c>
       <c r="E15" s="146" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14553,13 +14553,13 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="143"/>
       <c r="B16" s="144" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C16" s="145">
         <v>1.0</v>
       </c>
       <c r="D16" s="145" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E16" s="152"/>
       <c r="F16" s="144"/>
@@ -14578,9 +14578,15 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="143"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="145"/>
+      <c r="B17" s="144" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="145" t="s">
+        <v>652</v>
+      </c>
       <c r="E17" s="152"/>
       <c r="F17" s="144"/>
       <c r="G17" s="145"/>
@@ -14592,7 +14598,7 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>3280.0</v>
+        <v>3955.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14663,13 +14669,13 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="K21" s="165">
-        <v>8428.0</v>
+        <v>8547.0</v>
       </c>
       <c r="L21" s="166">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="M21" s="167" t="s">
         <v>657</v>
@@ -14727,13 +14733,13 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="K24" s="166">
-        <v>1363.0</v>
+        <v>1574.0</v>
       </c>
       <c r="L24" s="166">
-        <v>169.0</v>
+        <v>195.0</v>
       </c>
       <c r="M24" s="173">
         <v>21.0</v>
@@ -14793,10 +14799,10 @@
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.12405159314875214</v>
+        <v>0.13391607639866154</v>
       </c>
       <c r="M27" s="180">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14847,10 +14853,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8759484068512479</v>
+        <v>0.8660839236013385</v>
       </c>
       <c r="M30" s="184">
-        <v>0.06908715639365795</v>
+        <v>0.07539074960127592</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -15030,7 +15036,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="186"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="185"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15165,7 +15171,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="186"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="185"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -15205,7 +15211,7 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="185"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -15239,7 +15245,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="K10" s="185"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -15267,16 +15273,16 @@
       <c r="B11" s="4"/>
       <c r="C11" s="186"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="185"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="185"/>
+      <c r="J11" s="185"/>
       <c r="K11" s="185"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="N11" s="185"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="185"/>
@@ -15300,7 +15306,7 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="185"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -15402,7 +15408,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="186"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="185"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -15436,7 +15442,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="186"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="185"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -15470,7 +15476,7 @@
       <c r="B17" s="186"/>
       <c r="C17" s="186"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="185"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -15538,7 +15544,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="185"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15572,7 +15578,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="186"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="185"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -15640,7 +15646,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="185"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -15674,7 +15680,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="185"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15714,7 +15720,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
+      <c r="K24" s="185"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -15776,7 +15782,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="185"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15809,13 +15815,13 @@
       <c r="B27" s="186"/>
       <c r="C27" s="186"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="185"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="185"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -16013,13 +16019,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="185"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
+      <c r="K33" s="185"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16087,7 +16093,7 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="185"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
@@ -16121,7 +16127,7 @@
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="185"/>
+      <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
@@ -16183,7 +16189,7 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="185"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16217,7 +16223,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="185"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16257,7 +16263,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="185"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16284,7 +16290,7 @@
       <c r="B41" s="4"/>
       <c r="C41" s="186"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="185"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -16318,13 +16324,13 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="185"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
+      <c r="K42" s="185"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
@@ -16386,7 +16392,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="186"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="185"/>
+      <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -16420,7 +16426,7 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="185"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -16454,7 +16460,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="186"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="185"/>
+      <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -16556,7 +16562,7 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="185"/>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -16590,7 +16596,7 @@
       <c r="B50" s="4"/>
       <c r="C50" s="186"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="185"/>
+      <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -16624,7 +16630,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="185"/>
+      <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16658,13 +16664,13 @@
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="185"/>
+      <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="185"/>
+      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
@@ -16828,7 +16834,7 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="185"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -16902,7 +16908,7 @@
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
+      <c r="K59" s="185"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
@@ -16964,7 +16970,7 @@
       <c r="B61" s="4"/>
       <c r="C61" s="186"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="185"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -17004,7 +17010,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="185"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
@@ -17032,13 +17038,13 @@
       <c r="B63" s="4"/>
       <c r="C63" s="186"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="185"/>
+      <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-      <c r="K63" s="185"/>
+      <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
@@ -17066,7 +17072,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="186"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="185"/>
+      <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17096,22 +17102,22 @@
       <c r="AF64" s="185"/>
     </row>
     <row r="65">
-      <c r="A65" s="185"/>
-      <c r="B65" s="185"/>
-      <c r="C65" s="187"/>
-      <c r="D65" s="185"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="186"/>
+      <c r="D65" s="4"/>
       <c r="E65" s="185"/>
-      <c r="F65" s="185"/>
-      <c r="G65" s="185"/>
-      <c r="H65" s="185"/>
-      <c r="I65" s="185"/>
-      <c r="J65" s="185"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
       <c r="K65" s="185"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="185"/>
-      <c r="N65" s="185"/>
-      <c r="O65" s="185"/>
-      <c r="P65" s="185"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
       <c r="Q65" s="185"/>
       <c r="R65" s="185"/>
       <c r="S65" s="185"/>
@@ -17129,22 +17135,22 @@
       <c r="AF65" s="185"/>
     </row>
     <row r="66">
-      <c r="A66" s="185"/>
-      <c r="B66" s="185"/>
-      <c r="C66" s="187"/>
-      <c r="D66" s="185"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="186"/>
+      <c r="D66" s="4"/>
       <c r="E66" s="185"/>
-      <c r="F66" s="185"/>
-      <c r="G66" s="185"/>
-      <c r="H66" s="185"/>
-      <c r="I66" s="185"/>
-      <c r="J66" s="185"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
       <c r="K66" s="185"/>
-      <c r="L66" s="185"/>
-      <c r="M66" s="185"/>
-      <c r="N66" s="185"/>
-      <c r="O66" s="185"/>
-      <c r="P66" s="185"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
       <c r="Q66" s="185"/>
       <c r="R66" s="185"/>
       <c r="S66" s="185"/>
@@ -17163,22 +17169,22 @@
       <c r="AF66" s="185"/>
     </row>
     <row r="67">
-      <c r="A67" s="185"/>
-      <c r="B67" s="185"/>
-      <c r="C67" s="187"/>
-      <c r="D67" s="185"/>
-      <c r="E67" s="185"/>
-      <c r="F67" s="185"/>
-      <c r="G67" s="185"/>
-      <c r="H67" s="185"/>
-      <c r="I67" s="185"/>
-      <c r="J67" s="185"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="186"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
       <c r="K67" s="185"/>
-      <c r="L67" s="185"/>
-      <c r="M67" s="185"/>
-      <c r="N67" s="185"/>
-      <c r="O67" s="185"/>
-      <c r="P67" s="185"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
       <c r="Q67" s="185"/>
       <c r="R67" s="185"/>
       <c r="S67" s="185"/>
@@ -17196,22 +17202,22 @@
       <c r="AF67" s="185"/>
     </row>
     <row r="68">
-      <c r="A68" s="185"/>
-      <c r="B68" s="185"/>
-      <c r="C68" s="185"/>
-      <c r="D68" s="185"/>
-      <c r="E68" s="185"/>
-      <c r="F68" s="185"/>
-      <c r="G68" s="185"/>
-      <c r="H68" s="185"/>
-      <c r="I68" s="185"/>
-      <c r="J68" s="185"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
       <c r="K68" s="185"/>
-      <c r="L68" s="185"/>
-      <c r="M68" s="185"/>
-      <c r="N68" s="185"/>
-      <c r="O68" s="185"/>
-      <c r="P68" s="185"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
       <c r="Q68" s="185"/>
       <c r="R68" s="185"/>
       <c r="S68" s="185"/>
@@ -17230,22 +17236,22 @@
       <c r="AF68" s="185"/>
     </row>
     <row r="69">
-      <c r="A69" s="185"/>
-      <c r="B69" s="185"/>
-      <c r="C69" s="185"/>
-      <c r="D69" s="185"/>
-      <c r="E69" s="185"/>
-      <c r="F69" s="185"/>
-      <c r="G69" s="185"/>
-      <c r="H69" s="185"/>
-      <c r="I69" s="185"/>
-      <c r="J69" s="185"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
       <c r="K69" s="185"/>
-      <c r="L69" s="185"/>
-      <c r="M69" s="185"/>
-      <c r="N69" s="185"/>
-      <c r="O69" s="185"/>
-      <c r="P69" s="185"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
       <c r="Q69" s="185"/>
       <c r="R69" s="185"/>
       <c r="S69" s="185"/>
@@ -17264,22 +17270,22 @@
       <c r="AF69" s="185"/>
     </row>
     <row r="70">
-      <c r="A70" s="185"/>
-      <c r="B70" s="185"/>
-      <c r="C70" s="187"/>
-      <c r="D70" s="185"/>
-      <c r="E70" s="185"/>
-      <c r="F70" s="185"/>
-      <c r="G70" s="185"/>
-      <c r="H70" s="185"/>
-      <c r="I70" s="185"/>
-      <c r="J70" s="185"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="186"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
       <c r="K70" s="185"/>
-      <c r="L70" s="185"/>
-      <c r="M70" s="185"/>
-      <c r="N70" s="185"/>
-      <c r="O70" s="185"/>
-      <c r="P70" s="185"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
       <c r="Q70" s="185"/>
       <c r="R70" s="185"/>
       <c r="S70" s="185"/>
@@ -17298,22 +17304,22 @@
       <c r="AF70" s="185"/>
     </row>
     <row r="71">
-      <c r="A71" s="185"/>
-      <c r="B71" s="185"/>
-      <c r="C71" s="187"/>
-      <c r="D71" s="185"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="186"/>
+      <c r="D71" s="4"/>
       <c r="E71" s="185"/>
-      <c r="F71" s="185"/>
-      <c r="G71" s="185"/>
-      <c r="H71" s="185"/>
-      <c r="I71" s="185"/>
-      <c r="J71" s="185"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
       <c r="K71" s="185"/>
-      <c r="L71" s="185"/>
-      <c r="M71" s="185"/>
-      <c r="N71" s="185"/>
-      <c r="O71" s="185"/>
-      <c r="P71" s="185"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
       <c r="Q71" s="185"/>
       <c r="R71" s="185"/>
       <c r="S71" s="185"/>
@@ -17331,22 +17337,22 @@
       <c r="AF71" s="185"/>
     </row>
     <row r="72">
-      <c r="A72" s="185"/>
-      <c r="B72" s="185"/>
-      <c r="C72" s="185"/>
-      <c r="D72" s="185"/>
-      <c r="E72" s="185"/>
-      <c r="F72" s="185"/>
-      <c r="G72" s="185"/>
-      <c r="H72" s="185"/>
-      <c r="I72" s="185"/>
-      <c r="J72" s="185"/>
-      <c r="K72" s="185"/>
-      <c r="L72" s="185"/>
-      <c r="M72" s="185"/>
-      <c r="N72" s="185"/>
-      <c r="O72" s="185"/>
-      <c r="P72" s="185"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
       <c r="Q72" s="185"/>
       <c r="R72" s="185"/>
       <c r="S72" s="185"/>
@@ -17364,22 +17370,22 @@
       <c r="AF72" s="185"/>
     </row>
     <row r="73">
-      <c r="A73" s="185"/>
-      <c r="B73" s="185"/>
-      <c r="C73" s="187"/>
-      <c r="D73" s="185"/>
-      <c r="E73" s="185"/>
-      <c r="F73" s="185"/>
-      <c r="G73" s="185"/>
-      <c r="H73" s="185"/>
-      <c r="I73" s="185"/>
-      <c r="J73" s="185"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="186"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
       <c r="K73" s="185"/>
-      <c r="L73" s="185"/>
-      <c r="M73" s="185"/>
-      <c r="N73" s="185"/>
-      <c r="O73" s="185"/>
-      <c r="P73" s="185"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
       <c r="Q73" s="185"/>
       <c r="R73" s="185"/>
       <c r="S73" s="185"/>
@@ -17398,22 +17404,22 @@
       <c r="AF73" s="185"/>
     </row>
     <row r="74">
-      <c r="A74" s="185"/>
-      <c r="B74" s="187"/>
-      <c r="C74" s="187"/>
-      <c r="D74" s="185"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="186"/>
+      <c r="C74" s="186"/>
+      <c r="D74" s="4"/>
       <c r="E74" s="185"/>
-      <c r="F74" s="185"/>
-      <c r="G74" s="185"/>
-      <c r="H74" s="185"/>
-      <c r="I74" s="185"/>
-      <c r="J74" s="185"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
       <c r="K74" s="185"/>
-      <c r="L74" s="185"/>
-      <c r="M74" s="185"/>
-      <c r="N74" s="185"/>
-      <c r="O74" s="185"/>
-      <c r="P74" s="185"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
       <c r="Q74" s="185"/>
       <c r="R74" s="185"/>
       <c r="S74" s="185"/>
@@ -17432,22 +17438,22 @@
       <c r="AF74" s="185"/>
     </row>
     <row r="75">
-      <c r="A75" s="185"/>
-      <c r="B75" s="185"/>
-      <c r="C75" s="185"/>
-      <c r="D75" s="185"/>
-      <c r="E75" s="185"/>
-      <c r="F75" s="185"/>
-      <c r="G75" s="185"/>
-      <c r="H75" s="185"/>
-      <c r="I75" s="185"/>
-      <c r="J75" s="185"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
       <c r="K75" s="185"/>
-      <c r="L75" s="185"/>
-      <c r="M75" s="185"/>
-      <c r="N75" s="185"/>
-      <c r="O75" s="185"/>
-      <c r="P75" s="185"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
       <c r="Q75" s="185"/>
       <c r="R75" s="185"/>
       <c r="S75" s="185"/>
@@ -17466,22 +17472,22 @@
       <c r="AF75" s="185"/>
     </row>
     <row r="76">
-      <c r="A76" s="185"/>
-      <c r="B76" s="185"/>
-      <c r="C76" s="185"/>
-      <c r="D76" s="185"/>
-      <c r="E76" s="185"/>
-      <c r="F76" s="185"/>
-      <c r="G76" s="185"/>
-      <c r="H76" s="185"/>
-      <c r="I76" s="185"/>
-      <c r="J76" s="185"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
       <c r="K76" s="185"/>
-      <c r="L76" s="185"/>
-      <c r="M76" s="185"/>
-      <c r="N76" s="185"/>
-      <c r="O76" s="185"/>
-      <c r="P76" s="185"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
       <c r="Q76" s="185"/>
       <c r="R76" s="185"/>
       <c r="S76" s="185"/>
@@ -17500,22 +17506,22 @@
       <c r="AF76" s="185"/>
     </row>
     <row r="77">
-      <c r="A77" s="185"/>
-      <c r="B77" s="185"/>
-      <c r="C77" s="185"/>
-      <c r="D77" s="185"/>
-      <c r="E77" s="185"/>
-      <c r="F77" s="185"/>
-      <c r="G77" s="185"/>
-      <c r="H77" s="185"/>
-      <c r="I77" s="185"/>
-      <c r="J77" s="185"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
       <c r="K77" s="185"/>
-      <c r="L77" s="185"/>
-      <c r="M77" s="185"/>
-      <c r="N77" s="185"/>
-      <c r="O77" s="185"/>
-      <c r="P77" s="185"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
       <c r="Q77" s="185"/>
       <c r="R77" s="185"/>
       <c r="S77" s="185"/>
@@ -17529,26 +17535,27 @@
       <c r="AA77" s="185"/>
       <c r="AB77" s="185"/>
       <c r="AC77" s="185"/>
+      <c r="AD77" s="185"/>
       <c r="AE77" s="185"/>
       <c r="AF77" s="185"/>
     </row>
     <row r="78">
-      <c r="A78" s="185"/>
-      <c r="B78" s="185"/>
-      <c r="C78" s="187"/>
-      <c r="D78" s="185"/>
-      <c r="E78" s="185"/>
-      <c r="F78" s="185"/>
-      <c r="G78" s="185"/>
-      <c r="H78" s="185"/>
-      <c r="I78" s="185"/>
-      <c r="J78" s="185"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="186"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
       <c r="K78" s="185"/>
-      <c r="L78" s="185"/>
-      <c r="M78" s="185"/>
-      <c r="N78" s="185"/>
-      <c r="O78" s="185"/>
-      <c r="P78" s="185"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
       <c r="Q78" s="185"/>
       <c r="R78" s="185"/>
       <c r="S78" s="185"/>
@@ -17566,22 +17573,22 @@
       <c r="AF78" s="185"/>
     </row>
     <row r="79">
-      <c r="A79" s="185"/>
-      <c r="B79" s="185"/>
-      <c r="C79" s="187"/>
-      <c r="D79" s="185"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="186"/>
+      <c r="D79" s="4"/>
       <c r="E79" s="185"/>
-      <c r="F79" s="185"/>
-      <c r="G79" s="185"/>
-      <c r="H79" s="185"/>
-      <c r="I79" s="185"/>
-      <c r="J79" s="185"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
       <c r="K79" s="185"/>
-      <c r="L79" s="185"/>
-      <c r="M79" s="185"/>
-      <c r="N79" s="185"/>
-      <c r="O79" s="185"/>
-      <c r="P79" s="185"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
       <c r="Q79" s="185"/>
       <c r="R79" s="185"/>
       <c r="S79" s="185"/>
@@ -17600,22 +17607,22 @@
       <c r="AF79" s="185"/>
     </row>
     <row r="80">
-      <c r="A80" s="185"/>
-      <c r="B80" s="185"/>
-      <c r="C80" s="187"/>
-      <c r="D80" s="185"/>
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="186"/>
+      <c r="D80" s="4"/>
       <c r="E80" s="185"/>
-      <c r="F80" s="185"/>
-      <c r="G80" s="185"/>
-      <c r="H80" s="185"/>
-      <c r="I80" s="185"/>
-      <c r="J80" s="185"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
       <c r="K80" s="185"/>
-      <c r="L80" s="185"/>
-      <c r="M80" s="185"/>
-      <c r="N80" s="185"/>
-      <c r="O80" s="185"/>
-      <c r="P80" s="185"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
       <c r="Q80" s="185"/>
       <c r="R80" s="185"/>
       <c r="S80" s="185"/>
@@ -17633,22 +17640,22 @@
       <c r="AF80" s="185"/>
     </row>
     <row r="81">
-      <c r="A81" s="185"/>
-      <c r="B81" s="185"/>
-      <c r="C81" s="187"/>
-      <c r="D81" s="185"/>
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="186"/>
+      <c r="D81" s="4"/>
       <c r="E81" s="185"/>
-      <c r="F81" s="185"/>
-      <c r="G81" s="185"/>
-      <c r="H81" s="185"/>
-      <c r="I81" s="185"/>
-      <c r="J81" s="185"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
       <c r="K81" s="185"/>
-      <c r="L81" s="185"/>
-      <c r="M81" s="185"/>
-      <c r="N81" s="185"/>
-      <c r="O81" s="185"/>
-      <c r="P81" s="185"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
       <c r="Q81" s="185"/>
       <c r="R81" s="185"/>
       <c r="S81" s="185"/>
@@ -17667,22 +17674,22 @@
       <c r="AF81" s="185"/>
     </row>
     <row r="82">
-      <c r="A82" s="185"/>
-      <c r="B82" s="185"/>
-      <c r="C82" s="185"/>
-      <c r="D82" s="185"/>
-      <c r="E82" s="185"/>
-      <c r="F82" s="185"/>
-      <c r="G82" s="185"/>
-      <c r="H82" s="185"/>
-      <c r="I82" s="185"/>
-      <c r="J82" s="185"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
       <c r="K82" s="185"/>
-      <c r="L82" s="185"/>
-      <c r="M82" s="185"/>
-      <c r="N82" s="185"/>
-      <c r="O82" s="185"/>
-      <c r="P82" s="185"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
       <c r="Q82" s="185"/>
       <c r="R82" s="185"/>
       <c r="S82" s="185"/>
@@ -17701,22 +17708,22 @@
       <c r="AF82" s="185"/>
     </row>
     <row r="83">
-      <c r="A83" s="185"/>
-      <c r="B83" s="185"/>
-      <c r="C83" s="185"/>
-      <c r="D83" s="185"/>
-      <c r="E83" s="185"/>
-      <c r="F83" s="185"/>
-      <c r="G83" s="185"/>
-      <c r="H83" s="185"/>
-      <c r="I83" s="185"/>
-      <c r="J83" s="185"/>
-      <c r="K83" s="185"/>
-      <c r="L83" s="185"/>
-      <c r="M83" s="185"/>
-      <c r="N83" s="185"/>
-      <c r="O83" s="185"/>
-      <c r="P83" s="185"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
       <c r="Q83" s="185"/>
       <c r="R83" s="185"/>
       <c r="S83" s="185"/>
@@ -20734,7 +20741,7 @@
       </c>
       <c r="B28" s="192" t="str">
         <f>IF(OR(E28=Report!$B$1, F28=Report!$B$1, G28=Report!$B$1, H28=Report!$B$1), D28, "")</f>
-        <v/>
+        <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="C28" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -20756,7 +20763,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
         <v>Zličín</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="722">
   <si>
     <t>Datum</t>
   </si>
@@ -1938,13 +1938,13 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>148:00</t>
+    <t>252:00</t>
   </si>
   <si>
     <t>Šebesta Tomáš</t>
   </si>
   <si>
-    <t>79:00</t>
+    <t>160:30</t>
   </si>
   <si>
     <t>23:00</t>
@@ -1959,6 +1959,9 @@
     <t>Nováková Adéla</t>
   </si>
   <si>
+    <t>153:00</t>
+  </si>
+  <si>
     <t>13:00</t>
   </si>
   <si>
@@ -1977,13 +1980,16 @@
     <t>Putna Jaroslav</t>
   </si>
   <si>
+    <t>40:00</t>
+  </si>
+  <si>
     <t>7:00</t>
   </si>
   <si>
     <t>Ahurieva Viktoriia</t>
   </si>
   <si>
-    <t>22:00</t>
+    <t>31:00</t>
   </si>
   <si>
     <t>Gorol Patrik</t>
@@ -1992,7 +1998,16 @@
     <t>Coufal Jakub</t>
   </si>
   <si>
-    <t>11 min 51 s</t>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>33:00</t>
+  </si>
+  <si>
+    <t>11 min 54 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13271,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46164.0</v>
+        <v>46173.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13320,7 +13335,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Neděle</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -14173,18 +14188,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.35111359105567275</v>
+        <v>0.35782906539754117</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>652567.7999999999</v>
+        <v>958468.3999999999</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>233113.5</v>
+        <v>339494.89999999997</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14206,7 +14221,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>118961.0</v>
+        <v>169977.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14226,7 +14241,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>115758.0</v>
+        <v>173316.0</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14250,7 +14265,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>90413.3</v>
+        <v>132650.5</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14270,7 +14285,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>8211.0</v>
+        <v>10215.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14278,14 +14293,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>344.5</v>
+        <v>513</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14349,14 +14364,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>6.999999999989086</v>
+        <v>3.999999999974534</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>51318.0</v>
+        <v>78460.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14378,13 +14393,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="H10" s="145" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>92.0</v>
+        <v>152.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14402,7 +14417,7 @@
         <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="D11" s="145" t="s">
         <v>641</v>
@@ -14428,7 +14443,7 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>26427.0</v>
+        <v>40290.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
@@ -14438,22 +14453,22 @@
         <v>645</v>
       </c>
       <c r="C12" s="145">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F12" s="144" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G12" s="145">
         <v>1.0</v>
       </c>
       <c r="H12" s="145" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I12" s="147">
         <v>3.0</v>
@@ -14469,16 +14484,16 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
       <c r="B13" s="144" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C13" s="145">
         <v>3.0</v>
       </c>
       <c r="D13" s="145" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E13" s="146" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14490,23 +14505,23 @@
         <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>2700.0</v>
+        <v>4100.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
       <c r="B14" s="144" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C14" s="145">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D14" s="145" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E14" s="146" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14525,16 +14540,16 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="143"/>
       <c r="B15" s="144" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C15" s="145">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D15" s="145" t="s">
+        <v>656</v>
+      </c>
+      <c r="E15" s="146" t="s">
         <v>654</v>
-      </c>
-      <c r="E15" s="146" t="s">
-        <v>652</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14546,20 +14561,20 @@
         <v>610</v>
       </c>
       <c r="M15" s="120">
-        <v>71.0</v>
+        <v>190.0</v>
       </c>
       <c r="N15" s="116"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="143"/>
       <c r="B16" s="144" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C16" s="145">
         <v>1.0</v>
       </c>
       <c r="D16" s="145" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E16" s="152"/>
       <c r="F16" s="144"/>
@@ -14572,20 +14587,20 @@
         <v>611</v>
       </c>
       <c r="M16" s="120">
-        <v>1647.0</v>
+        <v>3124.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="143"/>
       <c r="B17" s="144" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C17" s="145">
         <v>1.0</v>
       </c>
       <c r="D17" s="145" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E17" s="152"/>
       <c r="F17" s="144"/>
@@ -14598,15 +14613,21 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>3955.0</v>
+        <v>6655.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="143"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="145"/>
-      <c r="D18" s="145"/>
+      <c r="B18" s="144" t="s">
+        <v>659</v>
+      </c>
+      <c r="C18" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="145" t="s">
+        <v>654</v>
+      </c>
       <c r="E18" s="152"/>
       <c r="F18" s="144"/>
       <c r="G18" s="145"/>
@@ -14620,9 +14641,15 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="143"/>
-      <c r="B19" s="144"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
+      <c r="B19" s="144" t="s">
+        <v>660</v>
+      </c>
+      <c r="C19" s="145">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="145" t="s">
+        <v>661</v>
+      </c>
       <c r="E19" s="152"/>
       <c r="F19" s="144"/>
       <c r="G19" s="145"/>
@@ -14669,16 +14696,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="K21" s="165">
-        <v>8547.0</v>
+        <v>13210.0</v>
       </c>
       <c r="L21" s="166">
-        <v>29.0</v>
+        <v>46.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14733,16 +14760,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="K24" s="166">
-        <v>1574.0</v>
+        <v>2327.0</v>
       </c>
       <c r="L24" s="166">
-        <v>195.0</v>
+        <v>274.0</v>
       </c>
       <c r="M24" s="173">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14795,14 +14822,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.13391607639866154</v>
+        <v>0.16953898073386703</v>
       </c>
       <c r="M27" s="180">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14853,10 +14880,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8660839236013385</v>
+        <v>0.8304610192661329</v>
       </c>
       <c r="M30" s="184">
-        <v>0.07539074960127592</v>
+        <v>0.07297063190892593</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14973,8 +15000,8 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -15143,7 +15170,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="185"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -15171,7 +15198,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="186"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="185"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -15211,7 +15238,7 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="K9" s="185"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -15273,16 +15300,16 @@
       <c r="B11" s="4"/>
       <c r="C11" s="186"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="185"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="185"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="185"/>
+      <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="185"/>
@@ -15306,7 +15333,7 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="185"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -15340,7 +15367,7 @@
       <c r="B13" s="4"/>
       <c r="C13" s="186"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="185"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -15510,7 +15537,7 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="185"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -15578,7 +15605,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="186"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="185"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -15612,7 +15639,7 @@
       <c r="B21" s="4"/>
       <c r="C21" s="186"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="185"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -15748,7 +15775,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="185"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15849,7 +15876,7 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="185"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -15883,7 +15910,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="185"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15917,7 +15944,7 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="185"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -15951,7 +15978,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="186"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="185"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -15985,7 +16012,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="186"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="185"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -16019,13 +16046,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="185"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="185"/>
+      <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16121,13 +16148,13 @@
       <c r="B36" s="4"/>
       <c r="C36" s="186"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="185"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
+      <c r="K36" s="185"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
@@ -16223,7 +16250,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="185"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16290,7 +16317,7 @@
       <c r="B41" s="4"/>
       <c r="C41" s="186"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="185"/>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -16324,7 +16351,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="185"/>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16364,7 +16391,7 @@
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="185"/>
+      <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
@@ -16432,7 +16459,7 @@
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="185"/>
+      <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -16500,7 +16527,7 @@
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-      <c r="K47" s="185"/>
+      <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -16528,7 +16555,7 @@
       <c r="B48" s="4"/>
       <c r="C48" s="186"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="185"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -16562,7 +16589,7 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="185"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -16636,7 +16663,7 @@
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="185"/>
+      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -16670,7 +16697,7 @@
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
+      <c r="K52" s="185"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
@@ -16698,7 +16725,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="185"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16766,7 +16793,7 @@
       <c r="B55" s="4"/>
       <c r="C55" s="186"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="185"/>
+      <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -16834,7 +16861,7 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="185"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -16902,7 +16929,7 @@
       <c r="B59" s="4"/>
       <c r="C59" s="186"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
+      <c r="E59" s="185"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -17010,7 +17037,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
+      <c r="K62" s="185"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
@@ -17044,7 +17071,7 @@
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
+      <c r="K63" s="185"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
@@ -17106,7 +17133,7 @@
       <c r="B65" s="4"/>
       <c r="C65" s="186"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="185"/>
+      <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -17139,7 +17166,7 @@
       <c r="B66" s="4"/>
       <c r="C66" s="186"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="185"/>
+      <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -17212,7 +17239,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-      <c r="K68" s="185"/>
+      <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
@@ -17246,7 +17273,7 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-      <c r="K69" s="185"/>
+      <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -17274,7 +17301,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="186"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="E70" s="185"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -17308,13 +17335,13 @@
       <c r="B71" s="4"/>
       <c r="C71" s="186"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="185"/>
+      <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-      <c r="K71" s="185"/>
+      <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
@@ -17341,13 +17368,13 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="185"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
+      <c r="K72" s="185"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
@@ -17408,13 +17435,13 @@
       <c r="B74" s="186"/>
       <c r="C74" s="186"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="185"/>
+      <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-      <c r="K74" s="185"/>
+      <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -17476,7 +17503,7 @@
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+      <c r="E76" s="185"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -17611,7 +17638,7 @@
       <c r="B80" s="4"/>
       <c r="C80" s="186"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="185"/>
+      <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
@@ -17644,13 +17671,13 @@
       <c r="B81" s="4"/>
       <c r="C81" s="186"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="185"/>
+      <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
-      <c r="K81" s="185"/>
+      <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
@@ -17718,7 +17745,7 @@
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
+      <c r="K83" s="185"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
@@ -17742,22 +17769,22 @@
       <c r="AF83" s="185"/>
     </row>
     <row r="84">
-      <c r="A84" s="185"/>
-      <c r="B84" s="185"/>
-      <c r="C84" s="187"/>
-      <c r="D84" s="185"/>
-      <c r="E84" s="185"/>
-      <c r="F84" s="185"/>
-      <c r="G84" s="185"/>
-      <c r="H84" s="185"/>
-      <c r="I84" s="185"/>
-      <c r="J84" s="185"/>
-      <c r="K84" s="185"/>
-      <c r="L84" s="185"/>
-      <c r="M84" s="185"/>
-      <c r="N84" s="185"/>
-      <c r="O84" s="185"/>
-      <c r="P84" s="185"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="186"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
       <c r="Q84" s="185"/>
       <c r="R84" s="185"/>
       <c r="S84" s="185"/>
@@ -17776,22 +17803,22 @@
       <c r="AF84" s="185"/>
     </row>
     <row r="85">
-      <c r="A85" s="185"/>
-      <c r="B85" s="185"/>
-      <c r="C85" s="187"/>
-      <c r="D85" s="185"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="186"/>
+      <c r="D85" s="4"/>
       <c r="E85" s="185"/>
-      <c r="F85" s="185"/>
-      <c r="G85" s="185"/>
-      <c r="H85" s="185"/>
-      <c r="I85" s="185"/>
-      <c r="J85" s="185"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
       <c r="K85" s="185"/>
-      <c r="L85" s="185"/>
-      <c r="M85" s="185"/>
-      <c r="N85" s="185"/>
-      <c r="O85" s="185"/>
-      <c r="P85" s="185"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
       <c r="Q85" s="185"/>
       <c r="R85" s="185"/>
       <c r="S85" s="185"/>
@@ -17809,22 +17836,22 @@
       <c r="AF85" s="185"/>
     </row>
     <row r="86">
-      <c r="A86" s="185"/>
-      <c r="B86" s="185"/>
-      <c r="C86" s="187"/>
-      <c r="D86" s="185"/>
-      <c r="E86" s="185"/>
-      <c r="F86" s="185"/>
-      <c r="G86" s="185"/>
-      <c r="H86" s="185"/>
-      <c r="I86" s="185"/>
-      <c r="J86" s="185"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="186"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
       <c r="K86" s="185"/>
-      <c r="L86" s="185"/>
-      <c r="M86" s="185"/>
-      <c r="N86" s="185"/>
-      <c r="O86" s="185"/>
-      <c r="P86" s="185"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
       <c r="Q86" s="185"/>
       <c r="R86" s="185"/>
       <c r="S86" s="185"/>
@@ -17838,6 +17865,7 @@
       <c r="AA86" s="185"/>
       <c r="AB86" s="185"/>
       <c r="AC86" s="185"/>
+      <c r="AD86" s="185"/>
       <c r="AE86" s="185"/>
       <c r="AF86" s="185"/>
     </row>
@@ -18325,6 +18353,7 @@
       <c r="O101" s="185"/>
       <c r="P101" s="185"/>
       <c r="Q101" s="185"/>
+      <c r="R101" s="185"/>
       <c r="S101" s="185"/>
       <c r="T101" s="185"/>
       <c r="U101" s="185"/>
@@ -18333,6 +18362,7 @@
       <c r="X101" s="185"/>
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
+      <c r="AA101" s="185"/>
       <c r="AB101" s="185"/>
       <c r="AC101" s="185"/>
       <c r="AE101" s="185"/>
@@ -18399,6 +18429,7 @@
       <c r="AA103" s="185"/>
       <c r="AB103" s="185"/>
       <c r="AC103" s="185"/>
+      <c r="AD103" s="185"/>
       <c r="AE103" s="185"/>
       <c r="AF103" s="185"/>
     </row>
@@ -18420,6 +18451,7 @@
       <c r="O104" s="185"/>
       <c r="P104" s="185"/>
       <c r="Q104" s="185"/>
+      <c r="R104" s="185"/>
       <c r="S104" s="185"/>
       <c r="T104" s="185"/>
       <c r="U104" s="185"/>
@@ -18428,6 +18460,7 @@
       <c r="X104" s="185"/>
       <c r="Y104" s="185"/>
       <c r="Z104" s="185"/>
+      <c r="AA104" s="185"/>
       <c r="AB104" s="185"/>
       <c r="AC104" s="185"/>
       <c r="AE104" s="185"/>
@@ -19250,10 +19283,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -20340,7 +20373,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="H21" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -20752,12 +20788,12 @@
         <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="E28" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F28" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
-      </c>
-      <c r="F28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
       </c>
       <c r="G28" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
@@ -26106,8 +26142,8 @@
         <v>0</v>
       </c>
       <c r="D126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pavel Břicháč")</f>
-        <v>Pavel Břicháč</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
+        <v>Břicháč Pavel</v>
       </c>
       <c r="E126" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -26162,8 +26198,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
+      <c r="D127" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
+        <v>Čerešňák Michal</v>
+      </c>
+      <c r="E127" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -26181,8 +26223,8 @@
       <c r="T127" s="2"/>
       <c r="U127" s="2"/>
       <c r="V127" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
+        <v>170</v>
       </c>
       <c r="W127" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -61046,7 +61088,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61078,28 +61120,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61128,22 +61170,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61165,20 +61207,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61202,18 +61244,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61240,15 +61282,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61275,14 +61317,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61306,14 +61348,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61338,17 +61380,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61373,14 +61415,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61593,7 +61635,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61918,7 +61960,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62039,7 +62081,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62158,7 +62200,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62192,7 +62234,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62284,7 +62326,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62463,7 +62505,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62584,7 +62626,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62792,7 +62834,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62913,7 +62955,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63121,7 +63163,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63590,7 +63632,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63624,7 +63666,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63658,7 +63700,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63692,7 +63734,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63785,7 +63827,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64051,7 +64093,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64085,7 +64127,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64177,7 +64219,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64240,7 +64282,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64332,7 +64374,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64366,7 +64408,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64400,7 +64442,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64463,7 +64505,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64555,7 +64597,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64618,7 +64660,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64739,7 +64781,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64890,7 +64932,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65275,7 +65317,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="705">
   <si>
     <t>Datum</t>
   </si>
@@ -1926,10 +1926,10 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Makula Radek</t>
-  </si>
-  <si>
-    <t>52:00</t>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>12:00</t>
   </si>
   <si>
     <t>29:00</t>
@@ -1938,76 +1938,25 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>252:00</t>
+    <t>14:00</t>
   </si>
   <si>
     <t>Šebesta Tomáš</t>
   </si>
   <si>
-    <t>160:30</t>
+    <t>9:00</t>
   </si>
   <si>
     <t>23:00</t>
   </si>
   <si>
-    <t>Kačena Stanislav</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>Nováková Adéla</t>
-  </si>
-  <si>
-    <t>153:00</t>
-  </si>
-  <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>Hanibal Filip</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>Kopic Jakub</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>Putna Jaroslav</t>
-  </si>
-  <si>
-    <t>40:00</t>
-  </si>
-  <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>Ahurieva Viktoriia</t>
-  </si>
-  <si>
-    <t>31:00</t>
-  </si>
-  <si>
-    <t>Gorol Patrik</t>
-  </si>
-  <si>
-    <t>Coufal Jakub</t>
-  </si>
-  <si>
-    <t>Yarushynskyi Vladyslav</t>
-  </si>
-  <si>
-    <t>Fáberová Kateřina</t>
-  </si>
-  <si>
-    <t>33:00</t>
-  </si>
-  <si>
-    <t>11 min 54 s</t>
+    <t>10 min 45 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13286,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46173.0</v>
+        <v>46176.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13335,7 +13284,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -14157,13 +14106,13 @@
         <v>Prosek</v>
       </c>
       <c r="C1" s="107">
-        <v>46143.0</v>
+        <v>46174.0</v>
       </c>
       <c r="D1" s="108" t="s">
         <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46173.0</v>
+        <v>46203.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14188,18 +14137,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.35782906539754117</v>
+        <v>0.48059530376512005</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>958468.3999999999</v>
+        <v>27695.899999999998</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>339494.89999999997</v>
+        <v>12560.599999999999</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14207,12 +14156,12 @@
       <c r="A3" s="117"/>
       <c r="B3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Pondělí</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Úterý</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14221,7 +14170,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>169977.0</v>
+        <v>8349.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14241,7 +14190,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>173316.0</v>
+        <v>1703.8</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14265,7 +14214,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>132650.5</v>
+        <v>1537.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14285,7 +14234,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>10215.0</v>
+        <v>0.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14293,14 +14242,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>513</v>
+        <v>21</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>279</v>
+        <v>14</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14364,14 +14313,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>3.999999999974534</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>78460.0</v>
+        <v>2338.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14381,7 +14330,7 @@
         <v>635</v>
       </c>
       <c r="C10" s="145">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="145" t="s">
         <v>636</v>
@@ -14393,13 +14342,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="H10" s="145" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>152.0</v>
+        <v>4.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14417,7 +14366,7 @@
         <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="145" t="s">
         <v>641</v>
@@ -14425,54 +14374,32 @@
       <c r="E11" s="146" t="s">
         <v>642</v>
       </c>
-      <c r="F11" s="144" t="s">
-        <v>643</v>
-      </c>
-      <c r="G11" s="145">
-        <v>3.0</v>
-      </c>
-      <c r="H11" s="145" t="s">
-        <v>644</v>
-      </c>
-      <c r="I11" s="147">
-        <v>7.0</v>
-      </c>
+      <c r="F11" s="144"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="147"/>
       <c r="J11" s="35"/>
       <c r="K11" s="20"/>
       <c r="L11" s="148" t="s">
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>40290.0</v>
+        <v>1030.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
-      <c r="B12" s="144" t="s">
-        <v>645</v>
-      </c>
-      <c r="C12" s="145">
-        <v>14.0</v>
-      </c>
-      <c r="D12" s="145" t="s">
-        <v>646</v>
-      </c>
+      <c r="B12" s="144"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
       <c r="E12" s="146" t="s">
-        <v>647</v>
-      </c>
-      <c r="F12" s="144" t="s">
-        <v>648</v>
-      </c>
-      <c r="G12" s="145">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="145" t="s">
-        <v>649</v>
-      </c>
-      <c r="I12" s="147">
-        <v>3.0</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="F12" s="144"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="147"/>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
@@ -14483,17 +14410,11 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
-      <c r="B13" s="144" t="s">
-        <v>650</v>
-      </c>
-      <c r="C13" s="145">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="145" t="s">
-        <v>651</v>
-      </c>
+      <c r="B13" s="144"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
       <c r="E13" s="146" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14505,23 +14426,17 @@
         <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>4100.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
-      <c r="B14" s="144" t="s">
-        <v>652</v>
-      </c>
-      <c r="C14" s="145">
-        <v>5.0</v>
-      </c>
-      <c r="D14" s="145" t="s">
-        <v>653</v>
-      </c>
+      <c r="B14" s="144"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
       <c r="E14" s="146" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14539,17 +14454,11 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="143"/>
-      <c r="B15" s="144" t="s">
-        <v>655</v>
-      </c>
-      <c r="C15" s="145">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="145" t="s">
-        <v>656</v>
-      </c>
+      <c r="B15" s="144"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
       <c r="E15" s="146" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14561,21 +14470,15 @@
         <v>610</v>
       </c>
       <c r="M15" s="120">
-        <v>190.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="116"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="143"/>
-      <c r="B16" s="144" t="s">
-        <v>657</v>
-      </c>
-      <c r="C16" s="145">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="145" t="s">
-        <v>654</v>
-      </c>
+      <c r="B16" s="144"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
       <c r="E16" s="152"/>
       <c r="F16" s="144"/>
       <c r="G16" s="145"/>
@@ -14587,21 +14490,15 @@
         <v>611</v>
       </c>
       <c r="M16" s="120">
-        <v>3124.0</v>
+        <v>0.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="143"/>
-      <c r="B17" s="144" t="s">
-        <v>658</v>
-      </c>
-      <c r="C17" s="145">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="145" t="s">
-        <v>654</v>
-      </c>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
       <c r="E17" s="152"/>
       <c r="F17" s="144"/>
       <c r="G17" s="145"/>
@@ -14613,21 +14510,15 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>6655.0</v>
+        <v>180.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="143"/>
-      <c r="B18" s="144" t="s">
-        <v>659</v>
-      </c>
-      <c r="C18" s="145">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="145" t="s">
-        <v>654</v>
-      </c>
+      <c r="B18" s="144"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
       <c r="E18" s="152"/>
       <c r="F18" s="144"/>
       <c r="G18" s="145"/>
@@ -14641,15 +14532,9 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="143"/>
-      <c r="B19" s="144" t="s">
-        <v>660</v>
-      </c>
-      <c r="C19" s="145">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="145" t="s">
-        <v>661</v>
-      </c>
+      <c r="B19" s="144"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
       <c r="E19" s="152"/>
       <c r="F19" s="144"/>
       <c r="G19" s="145"/>
@@ -14696,16 +14581,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="165">
-        <v>13210.0</v>
+        <v>0.0</v>
       </c>
       <c r="L21" s="166">
-        <v>46.0</v>
+        <v>0.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14760,16 +14645,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="166">
-        <v>2327.0</v>
+        <v>47.0</v>
       </c>
       <c r="L24" s="166">
-        <v>274.0</v>
+        <v>4.0</v>
       </c>
       <c r="M24" s="173">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14822,14 +14707,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.16953898073386703</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="180">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14880,10 +14765,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8304610192661329</v>
+        <v>1.0</v>
       </c>
       <c r="M30" s="184">
-        <v>0.07297063190892593</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14995,13 +14880,13 @@
       <c r="B2" s="4"/>
       <c r="C2" s="186"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="185"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="185"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -15063,7 +14948,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="186"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="185"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15164,7 +15049,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="186"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="185"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -15266,7 +15151,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="186"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="185"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -15300,7 +15185,7 @@
       <c r="B11" s="4"/>
       <c r="C11" s="186"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="185"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -15367,7 +15252,7 @@
       <c r="B13" s="4"/>
       <c r="C13" s="186"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="185"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -15441,7 +15326,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="185"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -15707,7 +15592,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="185"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15747,7 +15632,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="185"/>
+      <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -15809,7 +15694,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="185"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15842,7 +15727,7 @@
       <c r="B27" s="186"/>
       <c r="C27" s="186"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="185"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -15876,7 +15761,7 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="185"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -15910,7 +15795,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="185"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15978,7 +15863,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="186"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="185"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -16046,13 +15931,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="185"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
+      <c r="K33" s="185"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16114,7 +15999,7 @@
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="185"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -16216,7 +16101,7 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="185"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16284,7 +16169,7 @@
       <c r="B40" s="4"/>
       <c r="C40" s="186"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="185"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -16309,6 +16194,7 @@
       <c r="AA40" s="185"/>
       <c r="AB40" s="185"/>
       <c r="AC40" s="185"/>
+      <c r="AD40" s="185"/>
       <c r="AE40" s="185"/>
       <c r="AF40" s="185"/>
     </row>
@@ -16459,7 +16345,7 @@
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="185"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -16527,7 +16413,7 @@
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
+      <c r="K47" s="185"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -16555,13 +16441,13 @@
       <c r="B48" s="4"/>
       <c r="C48" s="186"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="185"/>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-      <c r="K48" s="185"/>
+      <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -16589,7 +16475,7 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="185"/>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -16663,7 +16549,7 @@
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
+      <c r="K51" s="185"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -16691,7 +16577,7 @@
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="185"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -16725,7 +16611,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="185"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16759,7 +16645,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="186"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="185"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -16827,7 +16713,7 @@
       <c r="B56" s="4"/>
       <c r="C56" s="186"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="185"/>
+      <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -16861,13 +16747,13 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="185"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="185"/>
+      <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -16929,7 +16815,7 @@
       <c r="B59" s="4"/>
       <c r="C59" s="186"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="185"/>
+      <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -16963,7 +16849,7 @@
       <c r="B60" s="4"/>
       <c r="C60" s="186"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="185"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -17065,7 +16951,7 @@
       <c r="B63" s="4"/>
       <c r="C63" s="186"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="185"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -17099,7 +16985,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="186"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="185"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17239,7 +17125,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
+      <c r="K68" s="185"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
@@ -17273,7 +17159,7 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="K69" s="185"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -17341,7 +17227,7 @@
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
+      <c r="K71" s="185"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
@@ -17441,7 +17327,7 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
+      <c r="K74" s="185"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -17604,7 +17490,7 @@
       <c r="B79" s="4"/>
       <c r="C79" s="186"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="185"/>
+      <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -17644,7 +17530,7 @@
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
-      <c r="K80" s="185"/>
+      <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
@@ -17671,13 +17557,13 @@
       <c r="B81" s="4"/>
       <c r="C81" s="186"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
+      <c r="E81" s="185"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
+      <c r="K81" s="185"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
@@ -17705,7 +17591,7 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="185"/>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -17739,16 +17625,16 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
+      <c r="E83" s="185"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="185"/>
+      <c r="I83" s="185"/>
+      <c r="J83" s="185"/>
+      <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
+      <c r="N83" s="185"/>
       <c r="O83" s="4"/>
       <c r="P83" s="4"/>
       <c r="Q83" s="185"/>
@@ -17773,13 +17659,13 @@
       <c r="B84" s="4"/>
       <c r="C84" s="186"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="185"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
+      <c r="K84" s="185"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
@@ -17807,7 +17693,7 @@
       <c r="B85" s="4"/>
       <c r="C85" s="186"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="185"/>
+      <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -17836,22 +17722,22 @@
       <c r="AF85" s="185"/>
     </row>
     <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="186"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
+      <c r="A86" s="185"/>
+      <c r="B86" s="185"/>
+      <c r="C86" s="187"/>
+      <c r="D86" s="185"/>
+      <c r="E86" s="185"/>
+      <c r="F86" s="185"/>
+      <c r="G86" s="185"/>
+      <c r="H86" s="185"/>
+      <c r="I86" s="185"/>
+      <c r="J86" s="185"/>
       <c r="K86" s="185"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
+      <c r="L86" s="185"/>
+      <c r="M86" s="185"/>
+      <c r="N86" s="185"/>
+      <c r="O86" s="185"/>
+      <c r="P86" s="185"/>
       <c r="Q86" s="185"/>
       <c r="R86" s="185"/>
       <c r="S86" s="185"/>
@@ -19283,10 +19169,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -19557,8 +19443,8 @@
         <v>Malešice</v>
       </c>
       <c r="G8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="H8" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -26255,8 +26141,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="D128" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
+        <v>Weindling Josef</v>
+      </c>
+      <c r="E128" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -26274,8 +26166,8 @@
       <c r="T128" s="2"/>
       <c r="U128" s="2"/>
       <c r="V128" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W128" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26306,8 +26198,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
+      <c r="D129" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
+        <v>Fux Vojtěch</v>
+      </c>
+      <c r="E129" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -26325,8 +26223,8 @@
       <c r="T129" s="2"/>
       <c r="U129" s="2"/>
       <c r="V129" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
+        <v>170</v>
       </c>
       <c r="W129" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -61088,7 +60986,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61120,28 +61018,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61170,22 +61068,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61207,20 +61105,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61244,18 +61142,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61282,15 +61180,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61317,14 +61215,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61348,14 +61246,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61380,17 +61278,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61415,14 +61313,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>691</v>
+        <v>674</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61635,7 +61533,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61960,7 +61858,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62081,7 +61979,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62200,7 +62098,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62234,7 +62132,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62326,7 +62224,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62505,7 +62403,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62626,7 +62524,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62834,7 +62732,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62955,7 +62853,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63163,7 +63061,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63632,7 +63530,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63666,7 +63564,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63700,7 +63598,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63734,7 +63632,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63827,7 +63725,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64093,7 +63991,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64127,7 +64025,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64219,7 +64117,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64282,7 +64180,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64374,7 +64272,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64408,7 +64306,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64442,7 +64340,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>715</v>
+        <v>698</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64505,7 +64403,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64597,7 +64495,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64660,7 +64558,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64781,7 +64679,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64932,7 +64830,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65317,7 +65215,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>
